--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9878.309999999999</v>
+        <v>9879.74</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6071</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="3">
@@ -850,18 +850,18 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0592</v>
+        <v>0.0593</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -870,18 +870,18 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0575</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0572</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="8">

--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9879.74</v>
+        <v>9891.379999999999</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.607</v>
+        <v>0.6063</v>
       </c>
     </row>
     <row r="3">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.0603</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0593</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="5">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0577</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="6">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0574</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="7">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0509</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="9">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="10">

--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -62,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -72,6 +80,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -152,12 +162,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -177,12 +187,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -202,12 +212,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -227,12 +237,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -252,12 +262,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>128</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -277,12 +287,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>159</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -302,12 +312,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -327,12 +337,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>221</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
+    <ext cx="8572499" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -642,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -700,7 +710,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9985.01</v>
+        <v>9926.040000000001</v>
       </c>
       <c r="C3" s="2">
         <f>B3-B2</f>
@@ -712,28 +722,6 @@
       </c>
       <c r="E3" s="3">
         <f>B3/$B$2-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>9891.379999999999</v>
-      </c>
-      <c r="C4" s="2">
-        <f>B4-B3</f>
-        <v/>
-      </c>
-      <c r="D4" s="3">
-        <f>B4/B3-1</f>
-        <v/>
-      </c>
-      <c r="E4" s="3">
-        <f>B4/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -746,12 +734,88 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B1:B221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Grafieken van vandaag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>iShares MSCI World (IWDA.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Micron (MU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Halfgeleider-ETF (SMH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>ASML (ASML.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Infineon (IFX.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>AMD (AMD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="24" customHeight="1">
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="24" customHeight="1">
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>Bitcoin (BTC-USD)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -810,7 +874,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6063</v>
+        <v>0.6067</v>
       </c>
     </row>
     <row r="3">
@@ -830,7 +894,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.0603</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="4">
@@ -850,18 +914,18 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0596</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -870,7 +934,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0576</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="6">
@@ -890,18 +954,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0575</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -910,18 +974,18 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.0574</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETH-USD</t>
+          <t>BTC-USD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -930,18 +994,18 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0511</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTC-USD</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,7 +1014,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="10">

--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9926.040000000001</v>
+        <v>9918.809999999999</v>
       </c>
       <c r="C3" s="2">
         <f>B3-B2</f>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6067</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="3">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0591</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="5">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0585</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="6">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0578</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="7">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0502</v>
+        <v>0.0501</v>
       </c>
     </row>
     <row r="10">

--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,11 +38,16 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="16"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -82,6 +87,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -167,7 +173,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -189,10 +195,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -214,10 +220,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -239,10 +245,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -264,10 +270,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>128</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -289,10 +295,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>159</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -314,10 +320,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>190</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -339,10 +345,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>221</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572499" cy="5143500"/>
+    <ext cx="8382000" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -652,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -710,7 +716,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9918.809999999999</v>
+        <v>9985.620000000001</v>
       </c>
       <c r="C3" s="2">
         <f>B3-B2</f>
@@ -722,6 +728,28 @@
       </c>
       <c r="E3" s="3">
         <f>B3/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>9816.290000000001</v>
+      </c>
+      <c r="C4" s="2">
+        <f>B4-B3</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>B4/B3-1</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>B4/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -736,14 +764,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B221"/>
+  <dimension ref="B1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="128" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Grafieken van vandaag</t>
@@ -751,68 +779,84 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>iShares MSCI World (IWDA.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Micron (MU)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Halfgeleider-ETF (SMH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="24" customHeight="1">
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>ASML (ASML.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Infineon (IFX.DE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>AMD (AMD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="24" customHeight="1">
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>Ethereum (ETH-USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="24" customHeight="1">
-      <c r="B221" s="6" t="inlineStr">
-        <is>
-          <t>Bitcoin (BTC-USD)</t>
-        </is>
-      </c>
-    </row>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>1. iShares MSCI World (IWDA.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="402" customHeight="1"/>
+    <row r="6" ht="30" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2. Micron (MU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="402" customHeight="1"/>
+    <row r="9" ht="30" customHeight="1"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>3. Halfgeleider-ETF (SMH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="402" customHeight="1"/>
+    <row r="12" ht="30" customHeight="1"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>4. ASML (ASML.AS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="402" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>5. Infineon (IFX.DE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="402" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1"/>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>6. AMD (AMD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="402" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1"/>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>7. Ethereum (ETH-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="402" customHeight="1"/>
+    <row r="24" ht="30" customHeight="1"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>8. Bitcoin (BTC-USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="402" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -874,7 +918,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6072</v>
+        <v>0.6113</v>
       </c>
     </row>
     <row r="3">
@@ -894,7 +938,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.0598</v>
+        <v>0.0587</v>
       </c>
     </row>
     <row r="4">
@@ -914,7 +958,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.059</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="5">
@@ -934,18 +978,18 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0584</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -954,18 +998,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0577</v>
+        <v>0.0574</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -974,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0574</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +1038,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0504</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="9">
@@ -1014,7 +1058,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0501</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="10">

--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verdeling" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafiekdata" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,7 +48,12 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000B0B0B"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="0052514E"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -86,8 +92,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,206 +173,1718 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$B$2:$B$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$C$2:$C$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$D$2:$D$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="135"/>
+          <min val="115"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="5"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$F$2:$F$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$G$2:$G$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$F$2:$F$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$F$2:$F$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$I$2:$I$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1200"/>
+          <min val="400"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="200"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$L$2:$L$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$M$2:$M$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$N$2:$N$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="650"/>
+          <min val="400"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="50"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Q1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$P$2:$P$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$Q$2:$Q$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!R1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$P$2:$P$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$R$2:$R$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!S1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$P$2:$P$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$S$2:$S$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1700"/>
+          <min val="1100"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="100"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!V1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$V$2:$V$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!W1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$W$2:$W$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!X1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$X$2:$X$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="80"/>
+          <min val="40"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AA1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$Z$2:$Z$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AA$2:$AA$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AB1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$Z$2:$Z$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AB$2:$AB$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AC1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$Z$2:$Z$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AC$2:$AC$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="700"/>
+          <min val="200"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="100"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AF1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$AE$2:$AE$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AF$2:$AF$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AG1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$AE$2:$AE$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AG$2:$AG$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AH1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$AE$2:$AE$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AH$2:$AH$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="3000"/>
+          <min val="1600"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="200"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AK1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="34925">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$AJ$2:$AJ$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AK$2:$AK$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AL1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$AJ$2:$AJ$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AL$2:$AL$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AM1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$AJ$2:$AJ$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AM$2:$AM$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="9"/>
+        <tickMarkSkip val="9"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="90000"/>
+          <min val="60000"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="5000"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>145</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>173</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>201</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8382000" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="9360000" cy="4140000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
@@ -738,7 +2259,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9816.290000000001</v>
+        <v>9817.969999999999</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -764,11 +2285,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B25"/>
+  <dimension ref="B1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="128" customWidth="1" min="2" max="2"/>
+    <col width="135" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -778,85 +2299,125 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke grafiek legt bovenaan in gewone taal uit hoe het ervoor staat, en onderaan hoe je hem leest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
+          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Ga met de muis over een lijn om de waarde te zien. Zwarte lijn = koers, blauw = gemiddelde van 50 dagen, oranje = van 200 dagen, rode stippellijn = stop-loss (daar verkoopt de bot).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>1. iShares MSCI World (IWDA.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="402" customHeight="1"/>
-    <row r="6" ht="30" customHeight="1"/>
-    <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>2. Micron (MU)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="402" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1"/>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>3. Halfgeleider-ETF (SMH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="402" customHeight="1"/>
-    <row r="12" ht="30" customHeight="1"/>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>4. ASML (ASML.AS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="402" customHeight="1"/>
-    <row r="15" ht="30" customHeight="1"/>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>5. Infineon (IFX.DE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="402" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>6. AMD (AMD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="402" customHeight="1"/>
-    <row r="21" ht="30" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>7. Ethereum (ETH-USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="402" customHeight="1"/>
-    <row r="24" ht="30" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>8. Bitcoin (BTC-USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="402" customHeight="1"/>
-    <row r="27" ht="30" customHeight="1"/>
+          <t>1. iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>2. Micron (MU)  ·  914,13 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Gestegen: 1,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>3. Halfgeleider-ETF (SMH)  ·  564,74 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Gedaald: -4,4% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>4. ASML (ASML.AS)  ·  1.528,20 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Gedaald: -4,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>5. Infineon (IFX.DE)  ·  55,35 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Gedaald: -14,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="24" customHeight="1">
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>6. AMD (AMD)  ·  570,82 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Gestegen: 7,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="24" customHeight="1">
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>7. Ethereum (ETH-USD)  ·  2.416,83 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>Gestegen: 28,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>8. Bitcoin (BTC-USD)  ·  81.674,80 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>Gestegen: 28,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -918,7 +2479,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6113</v>
+        <v>0.6112</v>
       </c>
     </row>
     <row r="3">
@@ -998,7 +2559,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0574</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="7">
@@ -1058,7 +2619,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0494</v>
+        <v>0.0496</v>
       </c>
     </row>
     <row r="10">
@@ -1528,4 +3089,7590 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AM66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>iShares MSCI World (IWDA.AS): Datum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Micron (MU): Datum</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Halfgeleider-ETF (SMH): Datum</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ASML (ASML.AS): Datum</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Infineon (IFX.DE): Datum</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>AMD (AMD): Datum</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD): Datum</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Bitcoin (BTC-USD): Datum</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Koers</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>126.29</v>
+      </c>
+      <c r="C2" t="n">
+        <v>123.3492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>114.7279</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>904.28</v>
+      </c>
+      <c r="H2" t="n">
+        <v>923.8603000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>476.0013</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>590.77</v>
+      </c>
+      <c r="M2" t="n">
+        <v>595.4148</v>
+      </c>
+      <c r="N2" t="n">
+        <v>436.9934</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1596.4774</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1496.5657</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1169.2299</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="W2" t="n">
+        <v>75.07899999999999</v>
+      </c>
+      <c r="X2" t="n">
+        <v>48.5648</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>529.14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>493.086</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>293.3068</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1881.3735</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1808.2342</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2039.3067</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>63551.875</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>63322.8705</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>69872.4305</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>126.26</v>
+      </c>
+      <c r="C3" t="n">
+        <v>123.4818</v>
+      </c>
+      <c r="D3" t="n">
+        <v>114.8231</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>853.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>929.3971</v>
+      </c>
+      <c r="I3" t="n">
+        <v>479.4822</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>568.92</v>
+      </c>
+      <c r="M3" t="n">
+        <v>596.6574000000001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>438.2339</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1535.1512</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1500.9125</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1172.5461</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="W3" t="n">
+        <v>75.119</v>
+      </c>
+      <c r="X3" t="n">
+        <v>48.7183</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>500.94</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>496.274</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>295.0142</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1878.135</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1812.4882</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2033.9537</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>63402.4336</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>63337.5587</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>69743.889</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="C4" t="n">
+        <v>123.5886</v>
+      </c>
+      <c r="D4" t="n">
+        <v>114.9072</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>848.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>933.574</v>
+      </c>
+      <c r="I4" t="n">
+        <v>482.9088</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>556.53</v>
+      </c>
+      <c r="M4" t="n">
+        <v>597.3342</v>
+      </c>
+      <c r="N4" t="n">
+        <v>439.4083</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1518.9708</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1505.2113</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1175.7691</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>64</v>
+      </c>
+      <c r="W4" t="n">
+        <v>75.1632</v>
+      </c>
+      <c r="X4" t="n">
+        <v>48.8719</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>495.76</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>499.084</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>296.6862</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1883.9913</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1817.7695</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2029.2941</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>63402.1719</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>63385.6995</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>69628.03879999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="C5" t="n">
+        <v>123.6952</v>
+      </c>
+      <c r="D5" t="n">
+        <v>114.9915</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>865.46</v>
+      </c>
+      <c r="H5" t="n">
+        <v>937.5535</v>
+      </c>
+      <c r="I5" t="n">
+        <v>486.4008</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>558.83</v>
+      </c>
+      <c r="M5" t="n">
+        <v>597.5155999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>440.5757</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1591.4834</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1511.7554</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1179.2691</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>75.35120000000001</v>
+      </c>
+      <c r="X5" t="n">
+        <v>49.0397</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>503.57</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>500.7276</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>298.3951</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1880.65</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1824.0862</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2024.0651</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>62975.5938</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>63450.7779</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>69501.5811</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>123.827</v>
+      </c>
+      <c r="D6" t="n">
+        <v>115.076</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>970.8200000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>944.0393</v>
+      </c>
+      <c r="I6" t="n">
+        <v>490.3456</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>584.08</v>
+      </c>
+      <c r="M6" t="n">
+        <v>598.3952</v>
+      </c>
+      <c r="N6" t="n">
+        <v>441.8328</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>1587.688</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1517.0011</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1182.862</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="X6" t="n">
+        <v>49.2193</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>544.4299999999999</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>503.447</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>300.2972</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>15 aug</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1880.9083</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1830.1721</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2018.3586</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>15 aug</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>63024.3203</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>63510.9357</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>69371.18979999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>126.03</v>
+      </c>
+      <c r="C7" t="n">
+        <v>123.939</v>
+      </c>
+      <c r="D7" t="n">
+        <v>115.1599</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>959.48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>948.295</v>
+      </c>
+      <c r="I7" t="n">
+        <v>494.2258</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>586.91</v>
+      </c>
+      <c r="M7" t="n">
+        <v>598.8026</v>
+      </c>
+      <c r="N7" t="n">
+        <v>443.0814</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>1577.3004</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1521.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1186.5172</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>75.4084</v>
+      </c>
+      <c r="X7" t="n">
+        <v>49.3777</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>552.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>505.3898</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>302.2102</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>16 aug</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>1873.943</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1836.2191</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2012.6952</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>16 aug</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>62818.6523</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>63568.5068</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>69239.3602</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>123.9872</v>
+      </c>
+      <c r="D8" t="n">
+        <v>115.2366</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>990.21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>952.1950000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>498.2386</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>580.17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>598.8798</v>
+      </c>
+      <c r="N8" t="n">
+        <v>444.3041</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>1561.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1526.3619</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1190.1014</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="W8" t="n">
+        <v>75.39279999999999</v>
+      </c>
+      <c r="X8" t="n">
+        <v>49.5333</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>539.6900000000001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>507.0078</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>304.0853</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1912.2021</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1843.056</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2008.1651</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>64506.2539</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>63667.9851</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>69139.0836</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="C9" t="n">
+        <v>124.0724</v>
+      </c>
+      <c r="D9" t="n">
+        <v>115.3129</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>920.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>955.2848</v>
+      </c>
+      <c r="I9" t="n">
+        <v>501.8895</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>561.1900000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>598.8786</v>
+      </c>
+      <c r="N9" t="n">
+        <v>445.3984</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>1429.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1529.7003</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1193.2073</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="W9" t="n">
+        <v>75.29600000000001</v>
+      </c>
+      <c r="X9" t="n">
+        <v>49.6767</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>508.481</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>305.6765</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1916.4596</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1849.181</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2004.2355</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v>64680.7109</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>63758.8317</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>69041.8438</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>124.1596</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115.3865</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>900.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>957.2186</v>
+      </c>
+      <c r="I10" t="n">
+        <v>505.4629</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>548.55</v>
+      </c>
+      <c r="M10" t="n">
+        <v>598.4004</v>
+      </c>
+      <c r="N10" t="n">
+        <v>446.4612</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1388.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1532.5183</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1195.9567</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="W10" t="n">
+        <v>75.15860000000001</v>
+      </c>
+      <c r="X10" t="n">
+        <v>49.8009</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>494.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>509.47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>307.0937</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>2251.458</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1862.8185</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2003.2673</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>69266.1875</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>63972.9783</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>68995.0692</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>125.18</v>
+      </c>
+      <c r="C11" t="n">
+        <v>124.2572</v>
+      </c>
+      <c r="D11" t="n">
+        <v>115.4728</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>820.53</v>
+      </c>
+      <c r="H11" t="n">
+        <v>958.1114</v>
+      </c>
+      <c r="I11" t="n">
+        <v>508.5838</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>597.4256</v>
+      </c>
+      <c r="N11" t="n">
+        <v>447.3842</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1362.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1533.1344</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1198.5622</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>74.88939999999999</v>
+      </c>
+      <c r="X11" t="n">
+        <v>49.9144</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>454.62</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>509.5684</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>308.189</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>2326.3848</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1877.167</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2003.5594</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>73032.75780000001</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>64233.5583</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>68975.36079999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>124.33</v>
+      </c>
+      <c r="C12" t="n">
+        <v>124.3162</v>
+      </c>
+      <c r="D12" t="n">
+        <v>115.5507</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>739</v>
+      </c>
+      <c r="H12" t="n">
+        <v>958.4005</v>
+      </c>
+      <c r="I12" t="n">
+        <v>511.3181</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>504.22</v>
+      </c>
+      <c r="M12" t="n">
+        <v>596.3832</v>
+      </c>
+      <c r="N12" t="n">
+        <v>448.1846</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>1440</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1535.0628</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1201.4256</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="W12" t="n">
+        <v>74.7188</v>
+      </c>
+      <c r="X12" t="n">
+        <v>50.0501</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>429.56</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>509.6776</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>309.1724</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>2515.2817</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1893.5093</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2004.4141</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>78335.1875</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>64570.556</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>68973.5929</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>123.69</v>
+      </c>
+      <c r="C13" t="n">
+        <v>124.3596</v>
+      </c>
+      <c r="D13" t="n">
+        <v>115.6281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>874.66</v>
+      </c>
+      <c r="H13" t="n">
+        <v>962.265</v>
+      </c>
+      <c r="I13" t="n">
+        <v>514.7843</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>538.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>596.2380000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>449.2574</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>1434.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1535.6006</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1204.2381</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="W13" t="n">
+        <v>74.4838</v>
+      </c>
+      <c r="X13" t="n">
+        <v>50.1991</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>485.39</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>510.9656</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>310.5248</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>22 aug</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>2424.2512</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1906.8639</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2005.3975</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>22 aug</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>77083.41409999999</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>64861.3403</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>68980.8422</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>124.23</v>
+      </c>
+      <c r="C14" t="n">
+        <v>124.3876</v>
+      </c>
+      <c r="D14" t="n">
+        <v>115.7046</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>823.03</v>
+      </c>
+      <c r="H14" t="n">
+        <v>964.7529</v>
+      </c>
+      <c r="I14" t="n">
+        <v>517.9365</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>540.53</v>
+      </c>
+      <c r="M14" t="n">
+        <v>596.1694</v>
+      </c>
+      <c r="N14" t="n">
+        <v>450.2666</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1419.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1535.4151</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1206.986</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="W14" t="n">
+        <v>74.1786</v>
+      </c>
+      <c r="X14" t="n">
+        <v>50.3451</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>476.15</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>512.2076</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>311.8235</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>23 aug</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>2463.8159</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1920.5596</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2006.9991</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>23 aug</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>77755.2656</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>65154.6795</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>69004.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>126.12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>124.4394</v>
+      </c>
+      <c r="D15" t="n">
+        <v>115.7914</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>829.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>966.7054000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>521.1497000000001</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>545.46</v>
+      </c>
+      <c r="M15" t="n">
+        <v>595.7854</v>
+      </c>
+      <c r="N15" t="n">
+        <v>451.3316</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1472.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1537.1045</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1209.8832</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="W15" t="n">
+        <v>73.902</v>
+      </c>
+      <c r="X15" t="n">
+        <v>50.4987</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>484.64</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>512.9488</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>313.1562</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>2481.8313</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1934.5361</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2010.2998</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>78964.4844</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65463.0116</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>69085.83199999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>124.5332</v>
+      </c>
+      <c r="D16" t="n">
+        <v>115.8921</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>892.67</v>
+      </c>
+      <c r="H16" t="n">
+        <v>969.3191</v>
+      </c>
+      <c r="I16" t="n">
+        <v>524.6541999999999</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>575.71</v>
+      </c>
+      <c r="M16" t="n">
+        <v>595.942</v>
+      </c>
+      <c r="N16" t="n">
+        <v>452.5065</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>1465.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1538.9256</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1212.7921</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="W16" t="n">
+        <v>73.569</v>
+      </c>
+      <c r="X16" t="n">
+        <v>50.638</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>518.58</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>514.3286000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>314.5561</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>2443.1594</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1947.4478</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2012.1987</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>78564.97659999999</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65754.4108</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>69125.8799</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>128.26</v>
+      </c>
+      <c r="C17" t="n">
+        <v>124.6406</v>
+      </c>
+      <c r="D17" t="n">
+        <v>115.9859</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>893.1900000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>972.1652</v>
+      </c>
+      <c r="I17" t="n">
+        <v>528.1085</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>569.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>595.8096</v>
+      </c>
+      <c r="N17" t="n">
+        <v>453.6438</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>1494</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1541.0191</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1215.9399</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>73.17319999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>50.7704</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>482.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>514.6194</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>315.7936</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>2506.261</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1962.2028</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2014.2773</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>79027.4219</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>66069.0113</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>69174.60709999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>128.12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>124.7396</v>
+      </c>
+      <c r="D18" t="n">
+        <v>116.0767</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>881.47</v>
+      </c>
+      <c r="H18" t="n">
+        <v>971.8798</v>
+      </c>
+      <c r="I18" t="n">
+        <v>531.505</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>571.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>595.1964</v>
+      </c>
+      <c r="N18" t="n">
+        <v>454.7924</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1499</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1543.3364</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1219.0252</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>72.79259999999999</v>
+      </c>
+      <c r="X18" t="n">
+        <v>50.906</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>489.28</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>514.3271999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>317.0746</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>2510.4102</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1977.5574</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2016.3855</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>80257.53909999999</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>66429.01059999999</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>69224.57120000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="C19" t="n">
+        <v>124.845</v>
+      </c>
+      <c r="D19" t="n">
+        <v>116.1734</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>877.5700000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>970.8658</v>
+      </c>
+      <c r="I19" t="n">
+        <v>534.86</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>582.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>594.9404</v>
+      </c>
+      <c r="N19" t="n">
+        <v>455.9752</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1513.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1545.7659</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1222.1512</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>62.53</v>
+      </c>
+      <c r="W19" t="n">
+        <v>72.4362</v>
+      </c>
+      <c r="X19" t="n">
+        <v>51.0489</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>483.36</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>514.0836</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>318.2886</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>2442.5359</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1991.5184</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2018.0803</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>77830.28909999999</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>66721.7534</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>69263.11870000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="C20" t="n">
+        <v>124.9454</v>
+      </c>
+      <c r="D20" t="n">
+        <v>116.2684</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>861</v>
+      </c>
+      <c r="H20" t="n">
+        <v>969.6183</v>
+      </c>
+      <c r="I20" t="n">
+        <v>538.1545</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>569.41</v>
+      </c>
+      <c r="M20" t="n">
+        <v>594.332</v>
+      </c>
+      <c r="N20" t="n">
+        <v>457.1011</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1554</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1547.6451</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1225.4102</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="W20" t="n">
+        <v>71.9332</v>
+      </c>
+      <c r="X20" t="n">
+        <v>51.1973</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>469.56</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>513.1130000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>319.4462</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>29 aug</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>2457.6863</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2004.7583</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2020.2713</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>29 aug</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>78245.8125</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>67004.1269</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>69310.378</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>125.0336</v>
+      </c>
+      <c r="D21" t="n">
+        <v>116.3589</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>868.52</v>
+      </c>
+      <c r="H21" t="n">
+        <v>967.5717</v>
+      </c>
+      <c r="I21" t="n">
+        <v>541.5057</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>572.9299999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>593.812</v>
+      </c>
+      <c r="N21" t="n">
+        <v>458.278</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>1567</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1549.3168</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1228.7297</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>63.09</v>
+      </c>
+      <c r="W21" t="n">
+        <v>71.435</v>
+      </c>
+      <c r="X21" t="n">
+        <v>51.3466</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>474.32</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>512.2773999999999</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>320.6667</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>30 aug</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>2417.9387</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2017.3551</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2022.6579</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>30 aug</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>77667.57030000001</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>67281.43769999999</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>69363.75599999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>125.1314</v>
+      </c>
+      <c r="D22" t="n">
+        <v>116.4461</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>911.29</v>
+      </c>
+      <c r="H22" t="n">
+        <v>965.0906</v>
+      </c>
+      <c r="I22" t="n">
+        <v>545.0297</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>584.83</v>
+      </c>
+      <c r="M22" t="n">
+        <v>593.3524</v>
+      </c>
+      <c r="N22" t="n">
+        <v>459.4835</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>1609.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1551.5808</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1232.2015</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>70.98399999999999</v>
+      </c>
+      <c r="X22" t="n">
+        <v>51.4889</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>482.93</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>511.7334</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>321.9064</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>2466.8203</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2030.5757</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2025.2573</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>78548.63280000001</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>67577.246</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>69425.39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>129.39</v>
+      </c>
+      <c r="C23" t="n">
+        <v>125.2418</v>
+      </c>
+      <c r="D23" t="n">
+        <v>116.5352</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>949.83</v>
+      </c>
+      <c r="H23" t="n">
+        <v>962.8085</v>
+      </c>
+      <c r="I23" t="n">
+        <v>548.6848</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>589.12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>592.4906</v>
+      </c>
+      <c r="N23" t="n">
+        <v>460.6789</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>1579.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1553.964</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1235.4343</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="W23" t="n">
+        <v>70.6726</v>
+      </c>
+      <c r="X23" t="n">
+        <v>51.6275</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>483.01</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>510.9628</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>323.0568</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>2417.842</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2043.4626</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2027.1038</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>77403.625</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>67880.5361</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>69468.1189</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="C24" t="n">
+        <v>125.352</v>
+      </c>
+      <c r="D24" t="n">
+        <v>116.6207</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>971.66</v>
+      </c>
+      <c r="H24" t="n">
+        <v>960.6536</v>
+      </c>
+      <c r="I24" t="n">
+        <v>552.4435999999999</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>587.8200000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>591.489</v>
+      </c>
+      <c r="N24" t="n">
+        <v>461.8238</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>1621.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1556.1325</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1238.9715</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="W24" t="n">
+        <v>70.3472</v>
+      </c>
+      <c r="X24" t="n">
+        <v>51.7668</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>514.39</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>510.4002</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>324.3304</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>2391.501</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2053.503</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2028.6313</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>77300.47659999999</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>68127.4234</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>69505.7831</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>128.72</v>
+      </c>
+      <c r="C25" t="n">
+        <v>125.4734</v>
+      </c>
+      <c r="D25" t="n">
+        <v>116.7047</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1011.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>960.9717000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>556.3939</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>594.0700000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>590.8198</v>
+      </c>
+      <c r="N25" t="n">
+        <v>462.9843</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1541.8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1556.8367</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1242.07</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>69.97880000000001</v>
+      </c>
+      <c r="X25" t="n">
+        <v>51.8822</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>506</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>510.0562</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>325.5704</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>2508.0208</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2065.3245</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2031.3412</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>81271.74219999999</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>68458.6107</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>69568.2009</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>127.42</v>
+      </c>
+      <c r="C26" t="n">
+        <v>125.6048</v>
+      </c>
+      <c r="D26" t="n">
+        <v>116.7829</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>940.76</v>
+      </c>
+      <c r="H26" t="n">
+        <v>962.5094</v>
+      </c>
+      <c r="I26" t="n">
+        <v>559.9657</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>569.77</v>
+      </c>
+      <c r="M26" t="n">
+        <v>590.8214</v>
+      </c>
+      <c r="N26" t="n">
+        <v>463.9958</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>1507.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1556.881</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1245.0398</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="W26" t="n">
+        <v>69.57640000000001</v>
+      </c>
+      <c r="X26" t="n">
+        <v>51.9868</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>484.39</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>510.4164</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>326.6707</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>2456.0781</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2077.1822</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2033.632</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>79671.9688</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>68776.2645</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>69622.345</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>126.99</v>
+      </c>
+      <c r="C27" t="n">
+        <v>125.7298</v>
+      </c>
+      <c r="D27" t="n">
+        <v>116.8581</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>937.11</v>
+      </c>
+      <c r="H27" t="n">
+        <v>962.2689</v>
+      </c>
+      <c r="I27" t="n">
+        <v>563.5323</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>560.92</v>
+      </c>
+      <c r="M27" t="n">
+        <v>590.0766</v>
+      </c>
+      <c r="N27" t="n">
+        <v>464.9874</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1505.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1555.5069</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1248.0553</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="W27" t="n">
+        <v>69.1434</v>
+      </c>
+      <c r="X27" t="n">
+        <v>52.0921</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>466.42</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>509.9382</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>327.7286</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>5 sep</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>2480.7356</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2089.9772</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2036.0747</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>5 sep</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>79823.86719999999</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>69094.75260000001</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>69683.9932</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>126.18</v>
+      </c>
+      <c r="C28" t="n">
+        <v>125.8356</v>
+      </c>
+      <c r="D28" t="n">
+        <v>116.9312</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>974.33</v>
+      </c>
+      <c r="H28" t="n">
+        <v>963.0405</v>
+      </c>
+      <c r="I28" t="n">
+        <v>567.2862</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>562.65</v>
+      </c>
+      <c r="M28" t="n">
+        <v>589.5094</v>
+      </c>
+      <c r="N28" t="n">
+        <v>465.9912</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1506</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1553.0741</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1251.13</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="W28" t="n">
+        <v>68.66160000000001</v>
+      </c>
+      <c r="X28" t="n">
+        <v>52.2023</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>469.46</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>509.8172</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>328.7953</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>6 sep</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>2514.5488</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2103.0403</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2038.8776</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>6 sep</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>80350.0469</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>69405.82150000001</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>69753.6168</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>126.51</v>
+      </c>
+      <c r="C29" t="n">
+        <v>125.9096</v>
+      </c>
+      <c r="D29" t="n">
+        <v>117.0051</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>966.78</v>
+      </c>
+      <c r="H29" t="n">
+        <v>964.5413</v>
+      </c>
+      <c r="I29" t="n">
+        <v>570.9477000000001</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>560.42</v>
+      </c>
+      <c r="M29" t="n">
+        <v>589.2996000000001</v>
+      </c>
+      <c r="N29" t="n">
+        <v>466.9684</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1550.4651</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1254.2456</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="W29" t="n">
+        <v>68.1298</v>
+      </c>
+      <c r="X29" t="n">
+        <v>52.3032</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>473.25</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>510.2342</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>329.8633</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>2490.958</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2115.4293</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2041.5913</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>79115.85159999999</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>69694.3224</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>69814.40850000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>126.23</v>
+      </c>
+      <c r="C30" t="n">
+        <v>125.9494</v>
+      </c>
+      <c r="D30" t="n">
+        <v>117.0851</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>910.4299999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>962.8356</v>
+      </c>
+      <c r="I30" t="n">
+        <v>574.4108</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>546.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>588.0466</v>
+      </c>
+      <c r="N30" t="n">
+        <v>467.9441</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>1501</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1548.6994</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1257.3382</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="W30" t="n">
+        <v>67.6412</v>
+      </c>
+      <c r="X30" t="n">
+        <v>52.4091</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>456.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>509.6002</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>330.8968</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>2484.9414</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2127.0529</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2044.1709</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>78438.5781</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>69958.49340000001</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>69866.57429999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>126.53</v>
+      </c>
+      <c r="C31" t="n">
+        <v>125.9972</v>
+      </c>
+      <c r="D31" t="n">
+        <v>117.174</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>932.97</v>
+      </c>
+      <c r="H31" t="n">
+        <v>961.8658</v>
+      </c>
+      <c r="I31" t="n">
+        <v>577.8893</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>555.8200000000001</v>
+      </c>
+      <c r="M31" t="n">
+        <v>586.7637999999999</v>
+      </c>
+      <c r="N31" t="n">
+        <v>468.9313</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>1497.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1545.5633</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1260.4127</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="W31" t="n">
+        <v>67.2038</v>
+      </c>
+      <c r="X31" t="n">
+        <v>52.5227</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>479.18</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>508.9524</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>332.011</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>2466.9138</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2137.8235</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2046.6368</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>78259.52340000001</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>70193.5814</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>69917.853</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C32" t="n">
+        <v>126.0464</v>
+      </c>
+      <c r="D32" t="n">
+        <v>117.2526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>938.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>958.8773</v>
+      </c>
+      <c r="I32" t="n">
+        <v>581.3908</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>555.77</v>
+      </c>
+      <c r="M32" t="n">
+        <v>584.9372</v>
+      </c>
+      <c r="N32" t="n">
+        <v>469.9601</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>1486.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1541.8116</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1263.4068</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="W32" t="n">
+        <v>66.70699999999999</v>
+      </c>
+      <c r="X32" t="n">
+        <v>52.6431</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>480.93</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>507.6258</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>333.2272</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>2437.0986</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2147.8957</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2049.0333</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>76568.125</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>70402.928</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>69962.3967</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>126.0968</v>
+      </c>
+      <c r="D33" t="n">
+        <v>117.3316</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>935.39</v>
+      </c>
+      <c r="H33" t="n">
+        <v>957.1731</v>
+      </c>
+      <c r="I33" t="n">
+        <v>584.8792999999999</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>573</v>
+      </c>
+      <c r="M33" t="n">
+        <v>584.0771999999999</v>
+      </c>
+      <c r="N33" t="n">
+        <v>471.0899</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>1494.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1538.5835</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1266.4922</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="W33" t="n">
+        <v>66.2092</v>
+      </c>
+      <c r="X33" t="n">
+        <v>52.7604</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>476.67</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>507.0134</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>334.4428</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>2514.7339</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2160.6484</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>2052.3294</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>77173.7969</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>70645.5077</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>70025.182</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>128.22</v>
+      </c>
+      <c r="C34" t="n">
+        <v>126.1648</v>
+      </c>
+      <c r="D34" t="n">
+        <v>117.4129</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>932.86</v>
+      </c>
+      <c r="H34" t="n">
+        <v>954.9697</v>
+      </c>
+      <c r="I34" t="n">
+        <v>588.2784</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>553.11</v>
+      </c>
+      <c r="M34" t="n">
+        <v>582.66</v>
+      </c>
+      <c r="N34" t="n">
+        <v>472.0671</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>1451.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1534.5433</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1269.4015</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="W34" t="n">
+        <v>65.61620000000001</v>
+      </c>
+      <c r="X34" t="n">
+        <v>52.8621</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>465.58</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>506.0754</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>335.5508</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>12 sep</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>2525.9446</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2173.9637</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2055.6943</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>12 sep</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>77270.4688</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>70908.9471</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>70091.1341</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="C35" t="n">
+        <v>126.1998</v>
+      </c>
+      <c r="D35" t="n">
+        <v>117.4943</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>958.73</v>
+      </c>
+      <c r="H35" t="n">
+        <v>951.468</v>
+      </c>
+      <c r="I35" t="n">
+        <v>591.8676</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>556.63</v>
+      </c>
+      <c r="M35" t="n">
+        <v>580.595</v>
+      </c>
+      <c r="N35" t="n">
+        <v>473.1004</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>1435.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1532.0728</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1272.2172</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="W35" t="n">
+        <v>65.11579999999999</v>
+      </c>
+      <c r="X35" t="n">
+        <v>52.9618</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>470.72</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>504.7424</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>336.7168</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>13 sep</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>2477.0208</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2186.0397</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2057.8063</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>13 sep</t>
+        </is>
+      </c>
+      <c r="AK35" t="n">
+        <v>76838.1562</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>71159.474</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>70135.5243</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>126.58</v>
+      </c>
+      <c r="C36" t="n">
+        <v>126.2516</v>
+      </c>
+      <c r="D36" t="n">
+        <v>117.5762</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>933.4400000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>945.9129</v>
+      </c>
+      <c r="I36" t="n">
+        <v>595.3115</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>545.22</v>
+      </c>
+      <c r="M36" t="n">
+        <v>578.1212</v>
+      </c>
+      <c r="N36" t="n">
+        <v>474.0544</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>1445.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1529.9502</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1275.1388</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="W36" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="X36" t="n">
+        <v>53.0655</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>459.61</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>502.902</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>337.7204</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>2514.407</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2197.2596</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2060.2444</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="AK36" t="n">
+        <v>78163.38280000001</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>71415.9356</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>70189.0723</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>126.79</v>
+      </c>
+      <c r="C37" t="n">
+        <v>126.2926</v>
+      </c>
+      <c r="D37" t="n">
+        <v>117.6614</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>956.08</v>
+      </c>
+      <c r="H37" t="n">
+        <v>944.0023</v>
+      </c>
+      <c r="I37" t="n">
+        <v>598.9083000000001</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>550.48</v>
+      </c>
+      <c r="M37" t="n">
+        <v>576.6898</v>
+      </c>
+      <c r="N37" t="n">
+        <v>475.088</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>1423.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1526.5766</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1277.8438</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="W37" t="n">
+        <v>64.1104</v>
+      </c>
+      <c r="X37" t="n">
+        <v>53.1725</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>457.06</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>501.6462</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>338.7659</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>2399.0869</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2207.4291</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2062.586</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
+        <v>75612.50780000001</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>71653.6878</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>70237.7259</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>127.88</v>
+      </c>
+      <c r="C38" t="n">
+        <v>126.3684</v>
+      </c>
+      <c r="D38" t="n">
+        <v>117.7593</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>958.16</v>
+      </c>
+      <c r="H38" t="n">
+        <v>942.1985</v>
+      </c>
+      <c r="I38" t="n">
+        <v>602.4662</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>552.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>575.3634</v>
+      </c>
+      <c r="N38" t="n">
+        <v>476.1315</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>1467.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1524.3985</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1280.7529</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="W38" t="n">
+        <v>63.6816</v>
+      </c>
+      <c r="X38" t="n">
+        <v>53.2932</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>456.16</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>500.3746</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>339.8127</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>2416.1199</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2217.3525</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2064.8413</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>76150.32030000001</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>71899.26700000001</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>70283.4982</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>127.44</v>
+      </c>
+      <c r="C39" t="n">
+        <v>126.4426</v>
+      </c>
+      <c r="D39" t="n">
+        <v>117.8536</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="H39" t="n">
+        <v>938.2628999999999</v>
+      </c>
+      <c r="I39" t="n">
+        <v>606.3406</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>567.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>573.966</v>
+      </c>
+      <c r="N39" t="n">
+        <v>477.2703</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>1500.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1522.2053</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1284.1047</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="W39" t="n">
+        <v>63.3326</v>
+      </c>
+      <c r="X39" t="n">
+        <v>53.4345</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>477.57</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>499.2746</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>340.9979</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>2447.1067</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2228.1243</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2067.3815</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>76403.77340000001</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>72149.17909999999</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>70336.8266</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>127.33</v>
+      </c>
+      <c r="C40" t="n">
+        <v>126.5118</v>
+      </c>
+      <c r="D40" t="n">
+        <v>117.9441</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1000.26</v>
+      </c>
+      <c r="H40" t="n">
+        <v>935.625</v>
+      </c>
+      <c r="I40" t="n">
+        <v>610.2005</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>573.73</v>
+      </c>
+      <c r="M40" t="n">
+        <v>573.2084</v>
+      </c>
+      <c r="N40" t="n">
+        <v>478.4777</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>1518</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1518.1787</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1287.421</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="W40" t="n">
+        <v>62.8682</v>
+      </c>
+      <c r="X40" t="n">
+        <v>53.5635</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>505.74</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>498.9578</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>342.3752</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>2611.3472</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2242.0038</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2070.3019</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
+        <v>80901.46090000001</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>72472.70209999999</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>70397.4546</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>127.16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>126.5524</v>
+      </c>
+      <c r="D41" t="n">
+        <v>118.0394</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1027.77</v>
+      </c>
+      <c r="H41" t="n">
+        <v>933.2782999999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>614.2109</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>574.29</v>
+      </c>
+      <c r="M41" t="n">
+        <v>572.0546000000001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>479.6572</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>1497.6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1515.3382</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1290.6279</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="W41" t="n">
+        <v>62.4492</v>
+      </c>
+      <c r="X41" t="n">
+        <v>53.6909</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>521.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>498.59</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>343.8629</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>19 sep</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>2631.9626</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2257.4361</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2073.5479</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>19 sep</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>81233.67969999999</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>72841.1008</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>70462.1548</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="C42" t="n">
+        <v>126.5562</v>
+      </c>
+      <c r="D42" t="n">
+        <v>118.122</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>977.41</v>
+      </c>
+      <c r="H42" t="n">
+        <v>929.7442</v>
+      </c>
+      <c r="I42" t="n">
+        <v>618.092</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>560.28</v>
+      </c>
+      <c r="M42" t="n">
+        <v>570.1424</v>
+      </c>
+      <c r="N42" t="n">
+        <v>480.8382</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>1474.2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1513.3042</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1293.474</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>62.0382</v>
+      </c>
+      <c r="X42" t="n">
+        <v>53.8069</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>503.6</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>497.0438</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>345.3508</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>20 sep</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
+        <v>2642.9976</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2273.4277</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2076.1303</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>20 sep</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
+        <v>81142.6094</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>73208.6866</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>70504.3149</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="C43" t="n">
+        <v>126.5604</v>
+      </c>
+      <c r="D43" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>975.26</v>
+      </c>
+      <c r="H43" t="n">
+        <v>928.607</v>
+      </c>
+      <c r="I43" t="n">
+        <v>621.9325</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>568.53</v>
+      </c>
+      <c r="M43" t="n">
+        <v>569.1038</v>
+      </c>
+      <c r="N43" t="n">
+        <v>482.0552</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>1478.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1510.2235</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1296.4013</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="W43" t="n">
+        <v>61.6618</v>
+      </c>
+      <c r="X43" t="n">
+        <v>53.9332</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>516.13</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>496.5488</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>346.9126</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>2776.4683</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2291.3066</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>2079.6547</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>86602.91409999999</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>73671.1048</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>70583.12390000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>126.64</v>
+      </c>
+      <c r="C44" t="n">
+        <v>126.5784</v>
+      </c>
+      <c r="D44" t="n">
+        <v>118.2779</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>924.03</v>
+      </c>
+      <c r="H44" t="n">
+        <v>927.5794</v>
+      </c>
+      <c r="I44" t="n">
+        <v>625.4340999999999</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>541.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>568.088</v>
+      </c>
+      <c r="N44" t="n">
+        <v>483.0724</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1505.4507</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1298.8447</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>61.1984</v>
+      </c>
+      <c r="X44" t="n">
+        <v>54.0308</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>493.41</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>496.0606</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>348.3044</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
+        <v>2752.6326</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2309.1941</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>2083.5241</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>86172.2812</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>74125.3325</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>70673.3028</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>126.43</v>
+      </c>
+      <c r="C45" t="n">
+        <v>126.58</v>
+      </c>
+      <c r="D45" t="n">
+        <v>118.3551</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>927.6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>926.4364</v>
+      </c>
+      <c r="I45" t="n">
+        <v>628.9505</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>542.11</v>
+      </c>
+      <c r="M45" t="n">
+        <v>566.8442</v>
+      </c>
+      <c r="N45" t="n">
+        <v>484.0881</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>1378.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1502.867</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1301.1272</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="W45" t="n">
+        <v>60.8684</v>
+      </c>
+      <c r="X45" t="n">
+        <v>54.1252</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>495.1036</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>349.7947</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
+        <v>2684.6919</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2325.5203</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>2087.1002</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>84383.00780000001</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>74531.87360000001</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>70758.85490000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>125.81</v>
+      </c>
+      <c r="C46" t="n">
+        <v>126.5882</v>
+      </c>
+      <c r="D46" t="n">
+        <v>118.4271</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>926.55</v>
+      </c>
+      <c r="H46" t="n">
+        <v>926.1998</v>
+      </c>
+      <c r="I46" t="n">
+        <v>632.4331</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>545.5599999999999</v>
+      </c>
+      <c r="M46" t="n">
+        <v>566.1264</v>
+      </c>
+      <c r="N46" t="n">
+        <v>485.0828</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>1396.2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1500.2478</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1303.4349</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>55</v>
+      </c>
+      <c r="W46" t="n">
+        <v>60.5624</v>
+      </c>
+      <c r="X46" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>495.0314</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>351.286</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>2687.3015</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2341.1358</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>2090.8537</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>84379.0625</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>74927.5048</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>70850.9013</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>126.47</v>
+      </c>
+      <c r="C47" t="n">
+        <v>126.6282</v>
+      </c>
+      <c r="D47" t="n">
+        <v>118.5046</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>977.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>926.7738000000001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>636.1394</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>560.61</v>
+      </c>
+      <c r="M47" t="n">
+        <v>565.4786</v>
+      </c>
+      <c r="N47" t="n">
+        <v>486.1299</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>1418</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1496.5903</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1305.7308</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="W47" t="n">
+        <v>60.1834</v>
+      </c>
+      <c r="X47" t="n">
+        <v>54.3163</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>545.09</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>495.585</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>352.9238</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
+        <v>2690.4756</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2356.9041</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2094.3414</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>84034.9219</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>75322.961</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>70929.064</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>126.6618</v>
+      </c>
+      <c r="D48" t="n">
+        <v>118.5867</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1015.8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>927.2569999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>640.0173</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>573</v>
+      </c>
+      <c r="M48" t="n">
+        <v>564.784</v>
+      </c>
+      <c r="N48" t="n">
+        <v>487.2356</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>1446</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1494.1681</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1308.197</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="W48" t="n">
+        <v>59.851</v>
+      </c>
+      <c r="X48" t="n">
+        <v>54.4181</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>559.8200000000001</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>495.847</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>354.6241</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>26 sep</t>
+        </is>
+      </c>
+      <c r="AF48" t="n">
+        <v>2695.2131</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2372.5428</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>2097.6319</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>26 sep</t>
+        </is>
+      </c>
+      <c r="AK48" t="n">
+        <v>84406.4531</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>75713.4863</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>71001.4616</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>127.05</v>
+      </c>
+      <c r="C49" t="n">
+        <v>126.6798</v>
+      </c>
+      <c r="D49" t="n">
+        <v>118.6667</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1043.96</v>
+      </c>
+      <c r="H49" t="n">
+        <v>928.5502</v>
+      </c>
+      <c r="I49" t="n">
+        <v>644.0408</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>596.03</v>
+      </c>
+      <c r="M49" t="n">
+        <v>564.484</v>
+      </c>
+      <c r="N49" t="n">
+        <v>488.4241</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>1481.4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1493.0171</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1310.8685</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="W49" t="n">
+        <v>59.6094</v>
+      </c>
+      <c r="X49" t="n">
+        <v>54.5272</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>615.52</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>496.9996</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>356.6255</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>27 sep</t>
+        </is>
+      </c>
+      <c r="AF49" t="n">
+        <v>2686.9268</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2387.9707</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>2100.8087</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>27 sep</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>84458.08590000001</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>76104.5542</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>71072.7277</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>128.62</v>
+      </c>
+      <c r="C50" t="n">
+        <v>126.7256</v>
+      </c>
+      <c r="D50" t="n">
+        <v>118.7534</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1096.16</v>
+      </c>
+      <c r="H50" t="n">
+        <v>931.7334</v>
+      </c>
+      <c r="I50" t="n">
+        <v>648.3519</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>607.46</v>
+      </c>
+      <c r="M50" t="n">
+        <v>564.9208</v>
+      </c>
+      <c r="N50" t="n">
+        <v>489.6452</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>1507.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1492.0866</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1313.6124</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="W50" t="n">
+        <v>59.3756</v>
+      </c>
+      <c r="X50" t="n">
+        <v>54.6468</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>623.77</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>498.7872</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>358.6564</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="AF50" t="n">
+        <v>2688.6687</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2403.5704</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>2103.8863</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>83502.6094</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>76477.7087</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>71137.77340000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>129.38</v>
+      </c>
+      <c r="C51" t="n">
+        <v>126.7914</v>
+      </c>
+      <c r="D51" t="n">
+        <v>118.8419</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1071.88</v>
+      </c>
+      <c r="H51" t="n">
+        <v>933.5086</v>
+      </c>
+      <c r="I51" t="n">
+        <v>652.5792</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>601.41</v>
+      </c>
+      <c r="M51" t="n">
+        <v>564.9428</v>
+      </c>
+      <c r="N51" t="n">
+        <v>490.8499</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>1515.8</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1491.4518</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1316.4495</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>58.57</v>
+      </c>
+      <c r="W51" t="n">
+        <v>59.2008</v>
+      </c>
+      <c r="X51" t="n">
+        <v>54.7535</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>614.61</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>500.1168</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>360.6495</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
+        <v>2676.7222</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>2419.6793</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2106.8071</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>83622.42969999999</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>76871.9455</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>71201.0442</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>126.8476</v>
+      </c>
+      <c r="D52" t="n">
+        <v>118.9298</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1080.53</v>
+      </c>
+      <c r="H52" t="n">
+        <v>937.0336</v>
+      </c>
+      <c r="I52" t="n">
+        <v>656.7969000000001</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>600.52</v>
+      </c>
+      <c r="M52" t="n">
+        <v>565.1378</v>
+      </c>
+      <c r="N52" t="n">
+        <v>492.0361</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>1503.2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1489.5863</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1319.2579</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="W52" t="n">
+        <v>59.0318</v>
+      </c>
+      <c r="X52" t="n">
+        <v>54.8482</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>629.26</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>502.1192</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>362.706</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="AF52" t="n">
+        <v>2683.6794</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2435.7254</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2109.7401</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>83553.85159999999</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>77271.98510000001</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>71262.7404</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="C53" t="n">
+        <v>126.8898</v>
+      </c>
+      <c r="D53" t="n">
+        <v>119.0135</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1082.28</v>
+      </c>
+      <c r="H53" t="n">
+        <v>941.6152</v>
+      </c>
+      <c r="I53" t="n">
+        <v>660.9749</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>606.5599999999999</v>
+      </c>
+      <c r="M53" t="n">
+        <v>565.8905999999999</v>
+      </c>
+      <c r="N53" t="n">
+        <v>493.2318</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>1522.6</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1489.3353</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1322.1887</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="W53" t="n">
+        <v>58.8928</v>
+      </c>
+      <c r="X53" t="n">
+        <v>54.9457</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>630.63</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>504.713</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>364.7536</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>2705.5371</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2452.2734</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>2112.3804</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>84853.10159999999</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>77700.9984</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>71323.0563</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="C54" t="n">
+        <v>126.971</v>
+      </c>
+      <c r="D54" t="n">
+        <v>119.1011</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1053.98</v>
+      </c>
+      <c r="H54" t="n">
+        <v>945.7157999999999</v>
+      </c>
+      <c r="I54" t="n">
+        <v>664.9838999999999</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>600.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>566.7602000000001</v>
+      </c>
+      <c r="N54" t="n">
+        <v>494.3926</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>1537</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1489.6958</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1325.2691</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="W54" t="n">
+        <v>58.7442</v>
+      </c>
+      <c r="X54" t="n">
+        <v>55.0464</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="AA54" t="n">
+        <v>607.87</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>506.9552</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>366.6848</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>2668.1511</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2467.9566</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>2113.9653</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>84497.21090000001</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>78122.8992</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>71371.2369</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>128.57</v>
+      </c>
+      <c r="C55" t="n">
+        <v>127.0372</v>
+      </c>
+      <c r="D55" t="n">
+        <v>119.1891</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1065.08</v>
+      </c>
+      <c r="H55" t="n">
+        <v>949.7082</v>
+      </c>
+      <c r="I55" t="n">
+        <v>668.9921000000001</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>606.9</v>
+      </c>
+      <c r="M55" t="n">
+        <v>567.7216</v>
+      </c>
+      <c r="N55" t="n">
+        <v>495.5624</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>1601.2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1489.8902</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1328.6422</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="W55" t="n">
+        <v>58.5794</v>
+      </c>
+      <c r="X55" t="n">
+        <v>55.1614</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>607.5700000000001</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>509.0352</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>368.6156</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>3 okt</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
+        <v>2687.2554</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2484.0887</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>2115.8113</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>3 okt</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>84763.5781</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>78558.65889999999</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>71425.4424</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="C56" t="n">
+        <v>127.0962</v>
+      </c>
+      <c r="D56" t="n">
+        <v>119.2811</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1065.11</v>
+      </c>
+      <c r="H56" t="n">
+        <v>951.5940000000001</v>
+      </c>
+      <c r="I56" t="n">
+        <v>673.0266</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>609</v>
+      </c>
+      <c r="M56" t="n">
+        <v>568.22</v>
+      </c>
+      <c r="N56" t="n">
+        <v>496.7587</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>1596.8</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1490.0724</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1332.1048</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>58.3734</v>
+      </c>
+      <c r="X56" t="n">
+        <v>55.2789</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>611.76</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>510.3818</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>370.5672</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>4 okt</t>
+        </is>
+      </c>
+      <c r="AF56" t="n">
+        <v>2726.509</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>2501.0007</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2118.4254</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>4 okt</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>86480.30469999999</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>79027.77860000001</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>71501.6161</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>129.15</v>
+      </c>
+      <c r="C57" t="n">
+        <v>127.1586</v>
+      </c>
+      <c r="D57" t="n">
+        <v>119.3744</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1097.39</v>
+      </c>
+      <c r="H57" t="n">
+        <v>954.3522</v>
+      </c>
+      <c r="I57" t="n">
+        <v>677.309</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>617.8099999999999</v>
+      </c>
+      <c r="M57" t="n">
+        <v>568.838</v>
+      </c>
+      <c r="N57" t="n">
+        <v>498.0826</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>1597</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1490.4664</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1335.7405</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="W57" t="n">
+        <v>58.252</v>
+      </c>
+      <c r="X57" t="n">
+        <v>55.398</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>615.73</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>511.6498</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>372.592</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="AF57" t="n">
+        <v>2711.0315</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2517.7425</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>2121.2935</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>85786.5938</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>79487.13740000001</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>71580.98510000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>128.81</v>
+      </c>
+      <c r="C58" t="n">
+        <v>127.2468</v>
+      </c>
+      <c r="D58" t="n">
+        <v>119.4698</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1074.89</v>
+      </c>
+      <c r="H58" t="n">
+        <v>956.0458</v>
+      </c>
+      <c r="I58" t="n">
+        <v>681.4971</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>630.6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>569.8466</v>
+      </c>
+      <c r="N58" t="n">
+        <v>499.4766</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>1653</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1492.304</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1339.5631</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="W58" t="n">
+        <v>58.2566</v>
+      </c>
+      <c r="X58" t="n">
+        <v>55.5426</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>633.91</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>513.5342000000001</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>374.7236</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="AF58" t="n">
+        <v>2697.5164</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>2533.4488</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2124.0486</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>85557.5625</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>79908.1636</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>71656.16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>130.05</v>
+      </c>
+      <c r="C59" t="n">
+        <v>127.3426</v>
+      </c>
+      <c r="D59" t="n">
+        <v>119.5736</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1063.96</v>
+      </c>
+      <c r="H59" t="n">
+        <v>958.9059999999999</v>
+      </c>
+      <c r="I59" t="n">
+        <v>685.6555</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>633.9</v>
+      </c>
+      <c r="M59" t="n">
+        <v>571.3008</v>
+      </c>
+      <c r="N59" t="n">
+        <v>500.8919</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>1656.2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1496.832</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1343.3575</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>63.47</v>
+      </c>
+      <c r="W59" t="n">
+        <v>58.2962</v>
+      </c>
+      <c r="X59" t="n">
+        <v>55.6858</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>631.75</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>515.7302</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>376.8365</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="AF59" t="n">
+        <v>2573.5273</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>2546.5902</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>2126.5328</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>83275.92969999999</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>80280.068</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>71728.982</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>131.18</v>
+      </c>
+      <c r="C60" t="n">
+        <v>127.4712</v>
+      </c>
+      <c r="D60" t="n">
+        <v>119.6774</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1045.5601</v>
+      </c>
+      <c r="H60" t="n">
+        <v>961.8132000000001</v>
+      </c>
+      <c r="I60" t="n">
+        <v>689.7568</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>632.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>572.9798</v>
+      </c>
+      <c r="N60" t="n">
+        <v>502.3634</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>1636.4</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1501.792</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1347.0808</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="W60" t="n">
+        <v>58.4344</v>
+      </c>
+      <c r="X60" t="n">
+        <v>55.8331</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>649.42</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>518.8196</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>379.0931</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
+        <v>2471.9126</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>2550.9992</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>2128.6271</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>81676.33590000001</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>80528.2709</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>71798.1376</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>131.87</v>
+      </c>
+      <c r="C61" t="n">
+        <v>127.605</v>
+      </c>
+      <c r="D61" t="n">
+        <v>119.782</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1088</v>
+      </c>
+      <c r="H61" t="n">
+        <v>967.1626</v>
+      </c>
+      <c r="I61" t="n">
+        <v>693.9553</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>625.03</v>
+      </c>
+      <c r="M61" t="n">
+        <v>574.8884</v>
+      </c>
+      <c r="N61" t="n">
+        <v>503.7577</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>1610.2</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1506.752</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1350.6372</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="W61" t="n">
+        <v>58.5638</v>
+      </c>
+      <c r="X61" t="n">
+        <v>55.9602</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>645.86</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>522.6444</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>381.3171</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="AF61" t="n">
+        <v>2485.5386</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>2554.1823</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>2130.2941</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>82546.32030000001</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>80718.5422</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>71856.29489999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="C62" t="n">
+        <v>127.7474</v>
+      </c>
+      <c r="D62" t="n">
+        <v>119.8834</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1035.84</v>
+      </c>
+      <c r="H62" t="n">
+        <v>973.0993999999999</v>
+      </c>
+      <c r="I62" t="n">
+        <v>697.8062</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>607.27</v>
+      </c>
+      <c r="M62" t="n">
+        <v>576.9494</v>
+      </c>
+      <c r="N62" t="n">
+        <v>505.0185</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>1630.6</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1510.564</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1354.3165</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="W62" t="n">
+        <v>58.5524</v>
+      </c>
+      <c r="X62" t="n">
+        <v>56.0728</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="AA62" t="n">
+        <v>620.6799999999999</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>526.4668</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>383.3533</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>10 okt</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
+        <v>2504.0278</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>2553.9572</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>2132.0357</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>10 okt</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>82912.22659999999</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>80810.083</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>71918.2668</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>130.98</v>
+      </c>
+      <c r="C63" t="n">
+        <v>127.8932</v>
+      </c>
+      <c r="D63" t="n">
+        <v>119.9813</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1029</v>
+      </c>
+      <c r="H63" t="n">
+        <v>976.1862</v>
+      </c>
+      <c r="I63" t="n">
+        <v>701.5696</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>603.33</v>
+      </c>
+      <c r="M63" t="n">
+        <v>578.2380000000001</v>
+      </c>
+      <c r="N63" t="n">
+        <v>506.2366</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>1601.6</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1513.912</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1357.812</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="W63" t="n">
+        <v>58.4962</v>
+      </c>
+      <c r="X63" t="n">
+        <v>56.1849</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>608.1</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>528.921</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>385.3191</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>11 okt</t>
+        </is>
+      </c>
+      <c r="AF63" t="n">
+        <v>2534.6992</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>2556.1662</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>2133.8691</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>11 okt</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>83679.4688</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>80942.00410000001</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>71980.11470000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>131.67</v>
+      </c>
+      <c r="C64" t="n">
+        <v>128.042</v>
+      </c>
+      <c r="D64" t="n">
+        <v>120.0822</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>989.04</v>
+      </c>
+      <c r="H64" t="n">
+        <v>979.5064</v>
+      </c>
+      <c r="I64" t="n">
+        <v>705.1348</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>590.99</v>
+      </c>
+      <c r="M64" t="n">
+        <v>579.2472</v>
+      </c>
+      <c r="N64" t="n">
+        <v>507.3758</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>1575.8</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1517.036</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1361.1208</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="W64" t="n">
+        <v>58.4112</v>
+      </c>
+      <c r="X64" t="n">
+        <v>56.2887</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>594.24</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>531.2828</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>387.2158</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="AF64" t="n">
+        <v>2444.3574</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>2555.777</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>2135.793</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>81762.5625</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>81022.14999999999</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>72044.9694</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="C65" t="n">
+        <v>128.1648</v>
+      </c>
+      <c r="D65" t="n">
+        <v>120.1856</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>953.1900000000001</v>
+      </c>
+      <c r="H65" t="n">
+        <v>981.9802</v>
+      </c>
+      <c r="I65" t="n">
+        <v>708.4687</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>588.12</v>
+      </c>
+      <c r="M65" t="n">
+        <v>580.1004</v>
+      </c>
+      <c r="N65" t="n">
+        <v>508.4955</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>1509.6</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1517.776</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1364.0836</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>56</v>
+      </c>
+      <c r="W65" t="n">
+        <v>58.2568</v>
+      </c>
+      <c r="X65" t="n">
+        <v>56.3815</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="AA65" t="n">
+        <v>605.53</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>533.7006</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>389.1682</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="AF65" t="n">
+        <v>2496.6255</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>2556.0729</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>2138.3197</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>83095.125</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>81104.7628</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>72128.7531</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>131.81</v>
+      </c>
+      <c r="C66" t="n">
+        <v>128.245</v>
+      </c>
+      <c r="D66" t="n">
+        <v>120.2857</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>914.13</v>
+      </c>
+      <c r="H66" t="n">
+        <v>982.4094</v>
+      </c>
+      <c r="I66" t="n">
+        <v>711.6168</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>564.74</v>
+      </c>
+      <c r="M66" t="n">
+        <v>579.881</v>
+      </c>
+      <c r="N66" t="n">
+        <v>509.4899</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>1528.2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1519.024</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1366.8165</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="W66" t="n">
+        <v>58.1622</v>
+      </c>
+      <c r="X66" t="n">
+        <v>56.4683</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="AA66" t="n">
+        <v>570.8200000000001</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>534.7454</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>390.9474</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="AF66" t="n">
+        <v>2416.8301</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>2555.5463</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>2140.4404</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>14 okt</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>81674.7969</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>81166.9592</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>72205.52860000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,21 +39,26 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="0052514E"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000B0B0B"/>
-      <sz val="14"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B0B0B"/>
+      <sz val="13"/>
     </font>
     <font>
       <color rgb="0052514E"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -92,11 +97,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,8 +526,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -913,8 +921,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1308,8 +1316,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1703,8 +1711,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2098,8 +2106,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2493,8 +2501,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2888,8 +2896,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3283,8 +3291,8 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -3339,10 +3347,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -3359,12 +3367,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -3383,10 +3391,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -3403,12 +3411,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -3427,10 +3435,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>122</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -3447,12 +3455,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>151</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -3471,10 +3479,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>180</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -3491,12 +3499,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>209</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4140000"/>
+    <ext cx="5580000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -3883,7 +3891,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9820.860000000001</v>
+        <v>9820.690000000001</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -3909,670 +3917,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B209"/>
+  <dimension ref="B1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="135" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Grafieken van vandaag</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Scroll naar beneden: alle grafieken staan onder elkaar. Elke kaars is één handelsdag: groen = die dag gestegen, rood = die dag gedaald; de dunne streep is de hoogste en laagste koers. Blauwe lijn = gemiddelde van 50 dagen, oranje = van 200 dagen, grijze stippellijn = instap, rode stippellijn = stop-loss (daar verkoopt de bot). Ga met de muis over een kaars of lijn voor de waarde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>1. iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="B2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00008300"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>▮ groen</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
+            <t xml:space="preserve"> = dag gestegen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00E34948"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>▮ rood</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
+            <t xml:space="preserve"> = dag gedaald    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="002A78D6"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>━ blauw</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
+            <t xml:space="preserve"> = gemiddelde 50 dagen    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00EB6834"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>━ oranje</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
+            <t xml:space="preserve"> = gemiddelde 200 dagen    </t>
           </r>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>2. Micron (MU)  ·  914,13 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Gestegen: 1,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
             </rPr>
-            <t>▮ groen</t>
+            <t>╌ grijs</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
+            <t xml:space="preserve"> = instap    </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="00E34948"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t>▮ rood</t>
+            <t>╌ rood</t>
           </r>
           <r>
             <rPr>
               <color rgb="0052514E"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
+            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
           </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>3. Halfgeleider-ETF (SMH)  ·  564,74 USD</t>
+    <row r="3">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Elke kaars is één handelsdag; het dunne streepje loopt van de laagste naar de hoogste koers van die dag. Ga met de muis over een kaars of lijn om de waarde te zien.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="8" t="inlineStr">
+    <row r="5" ht="26" customHeight="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Investeerder: beleggingen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Micron (MU)  ·  914,13 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Gestegen: 1,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Halfgeleider-ETF (SMH)  ·  564,74 USD</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>ASML (ASML.AS)  ·  1.528,20 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Gedaald: -4,4% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Gedaald: -4,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+        </is>
+      </c>
     </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Infineon (IFX.DE)  ·  55,35 EUR</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>AMD (AMD)  ·  570,82 USD</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="24" customHeight="1">
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>4. ASML (ASML.AS)  ·  1.528,20 EUR</t>
+    <row r="49" ht="30" customHeight="1">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Gedaald: -14,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Gestegen: 7,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Gedaald: -4,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Ethereum (ETH-USD)  ·  2.422,78 USD</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Bitcoin (BTC-USD)  ·  81.779,10 USD</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>5. Infineon (IFX.DE)  ·  55,35 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>Gedaald: -14,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="24" customHeight="1">
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>6. AMD (AMD)  ·  570,82 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="8" t="inlineStr">
-        <is>
-          <t>Gestegen: 7,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="24" customHeight="1">
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>7. Ethereum (ETH-USD)  ·  2.423,80 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="B179" s="8" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>Gestegen: 28,8% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
-    </row>
-    <row r="180">
-      <c r="B180" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="24" customHeight="1">
-      <c r="B207" s="7" t="inlineStr">
-        <is>
-          <t>8. Bitcoin (BTC-USD)  ·  81.822,76 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="B208" s="8" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>Gestegen: 28,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="B209" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00008300"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ groen</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gestegen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00E34948"/>
-              <sz val="11"/>
-            </rPr>
-            <t>▮ rood</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = dag gedaald   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="002A78D6"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ blauw</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 50 dagen   </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00EB6834"/>
-              <sz val="11"/>
-            </rPr>
-            <t>━ oranje</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="0052514E"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> = gemiddelde 200 dagen   </t>
-          </r>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -5537,26 +5106,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15 jul</t>
+          <t>16 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126.42</v>
+        <v>126.06</v>
       </c>
       <c r="C2" t="n">
-        <v>126.64</v>
+        <v>126.29</v>
       </c>
       <c r="D2" t="n">
-        <v>126.12</v>
+        <v>125.5</v>
       </c>
       <c r="E2" t="n">
-        <v>126.29</v>
+        <v>126.26</v>
       </c>
       <c r="F2" t="n">
-        <v>123.3492</v>
+        <v>123.4818</v>
       </c>
       <c r="G2" t="n">
-        <v>114.7279</v>
+        <v>114.8231</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -5723,26 +5292,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126.06</v>
+        <v>124.66</v>
       </c>
       <c r="C3" t="n">
-        <v>126.29</v>
+        <v>125.18</v>
       </c>
       <c r="D3" t="n">
-        <v>125.5</v>
+        <v>124.27</v>
       </c>
       <c r="E3" t="n">
-        <v>126.26</v>
+        <v>124.85</v>
       </c>
       <c r="F3" t="n">
-        <v>123.4818</v>
+        <v>123.5886</v>
       </c>
       <c r="G3" t="n">
-        <v>114.8231</v>
+        <v>114.9072</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -5909,26 +5478,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>124.77</v>
+      </c>
+      <c r="C4" t="n">
+        <v>125.63</v>
+      </c>
+      <c r="D4" t="n">
         <v>124.66</v>
       </c>
-      <c r="C4" t="n">
-        <v>125.18</v>
-      </c>
-      <c r="D4" t="n">
-        <v>124.27</v>
-      </c>
       <c r="E4" t="n">
-        <v>124.85</v>
+        <v>125.26</v>
       </c>
       <c r="F4" t="n">
-        <v>123.5886</v>
+        <v>123.6952</v>
       </c>
       <c r="G4" t="n">
-        <v>114.9072</v>
+        <v>114.9915</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -6095,26 +5664,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>124.77</v>
+        <v>125.34</v>
       </c>
       <c r="C5" t="n">
-        <v>125.63</v>
+        <v>125.75</v>
       </c>
       <c r="D5" t="n">
-        <v>124.66</v>
+        <v>125.05</v>
       </c>
       <c r="E5" t="n">
-        <v>125.26</v>
+        <v>125.75</v>
       </c>
       <c r="F5" t="n">
-        <v>123.6952</v>
+        <v>123.827</v>
       </c>
       <c r="G5" t="n">
-        <v>114.9915</v>
+        <v>115.076</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -6281,26 +5850,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.34</v>
+        <v>125.39</v>
       </c>
       <c r="C6" t="n">
-        <v>125.75</v>
+        <v>126.08</v>
       </c>
       <c r="D6" t="n">
-        <v>125.05</v>
+        <v>125.3</v>
       </c>
       <c r="E6" t="n">
-        <v>125.75</v>
+        <v>126.03</v>
       </c>
       <c r="F6" t="n">
-        <v>123.827</v>
+        <v>123.939</v>
       </c>
       <c r="G6" t="n">
-        <v>115.076</v>
+        <v>115.1599</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -6467,26 +6036,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125.39</v>
+        <v>125.34</v>
       </c>
       <c r="C7" t="n">
-        <v>126.08</v>
+        <v>125.59</v>
       </c>
       <c r="D7" t="n">
-        <v>125.3</v>
+        <v>124.27</v>
       </c>
       <c r="E7" t="n">
-        <v>126.03</v>
+        <v>124.4</v>
       </c>
       <c r="F7" t="n">
-        <v>123.939</v>
+        <v>123.9872</v>
       </c>
       <c r="G7" t="n">
-        <v>115.1599</v>
+        <v>115.2366</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -6653,26 +6222,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>125.34</v>
+        <v>124.62</v>
       </c>
       <c r="C8" t="n">
-        <v>125.59</v>
+        <v>125.39</v>
       </c>
       <c r="D8" t="n">
-        <v>124.27</v>
+        <v>124.57</v>
       </c>
       <c r="E8" t="n">
-        <v>124.4</v>
+        <v>125.26</v>
       </c>
       <c r="F8" t="n">
-        <v>123.9872</v>
+        <v>124.0724</v>
       </c>
       <c r="G8" t="n">
-        <v>115.2366</v>
+        <v>115.3129</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -6839,26 +6408,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124.62</v>
+        <v>125.76</v>
       </c>
       <c r="C9" t="n">
-        <v>125.39</v>
+        <v>125.97</v>
       </c>
       <c r="D9" t="n">
-        <v>124.57</v>
+        <v>124.73</v>
       </c>
       <c r="E9" t="n">
-        <v>125.26</v>
+        <v>124.75</v>
       </c>
       <c r="F9" t="n">
-        <v>124.0724</v>
+        <v>124.1596</v>
       </c>
       <c r="G9" t="n">
-        <v>115.3129</v>
+        <v>115.3865</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7025,26 +6594,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125.76</v>
+        <v>124.82</v>
       </c>
       <c r="C10" t="n">
-        <v>125.97</v>
+        <v>125.24</v>
       </c>
       <c r="D10" t="n">
-        <v>124.73</v>
+        <v>124.53</v>
       </c>
       <c r="E10" t="n">
-        <v>124.75</v>
+        <v>125.18</v>
       </c>
       <c r="F10" t="n">
-        <v>124.1596</v>
+        <v>124.2572</v>
       </c>
       <c r="G10" t="n">
-        <v>115.3865</v>
+        <v>115.4728</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -7211,26 +6780,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>124.82</v>
+        <v>125.36</v>
       </c>
       <c r="C11" t="n">
-        <v>125.24</v>
+        <v>125.48</v>
       </c>
       <c r="D11" t="n">
-        <v>124.53</v>
+        <v>124.05</v>
       </c>
       <c r="E11" t="n">
-        <v>125.18</v>
+        <v>124.33</v>
       </c>
       <c r="F11" t="n">
-        <v>124.2572</v>
+        <v>124.3162</v>
       </c>
       <c r="G11" t="n">
-        <v>115.4728</v>
+        <v>115.5507</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -7397,26 +6966,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125.36</v>
+        <v>123.55</v>
       </c>
       <c r="C12" t="n">
-        <v>125.48</v>
+        <v>124.08</v>
       </c>
       <c r="D12" t="n">
-        <v>124.05</v>
+        <v>123.17</v>
       </c>
       <c r="E12" t="n">
-        <v>124.33</v>
+        <v>123.69</v>
       </c>
       <c r="F12" t="n">
-        <v>124.3162</v>
+        <v>124.3596</v>
       </c>
       <c r="G12" t="n">
-        <v>115.5507</v>
+        <v>115.6281</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7583,26 +7152,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>123.55</v>
+        <v>124.77</v>
       </c>
       <c r="C13" t="n">
-        <v>124.08</v>
+        <v>125.22</v>
       </c>
       <c r="D13" t="n">
-        <v>123.17</v>
+        <v>123.95</v>
       </c>
       <c r="E13" t="n">
-        <v>123.69</v>
+        <v>124.23</v>
       </c>
       <c r="F13" t="n">
-        <v>124.3596</v>
+        <v>124.3876</v>
       </c>
       <c r="G13" t="n">
-        <v>115.6281</v>
+        <v>115.7046</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7671,7 +7240,7 @@
         <v>1535.6006</v>
       </c>
       <c r="AE13" t="n">
-        <v>1204.2381</v>
+        <v>1204.238</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -7769,26 +7338,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>124.77</v>
+        <v>125.4</v>
       </c>
       <c r="C14" t="n">
-        <v>125.22</v>
+        <v>126.2</v>
       </c>
       <c r="D14" t="n">
-        <v>123.95</v>
+        <v>125.1</v>
       </c>
       <c r="E14" t="n">
-        <v>124.23</v>
+        <v>126.12</v>
       </c>
       <c r="F14" t="n">
-        <v>124.3876</v>
+        <v>124.4394</v>
       </c>
       <c r="G14" t="n">
-        <v>115.7046</v>
+        <v>115.7914</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7955,26 +7524,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125.4</v>
+        <v>126.84</v>
       </c>
       <c r="C15" t="n">
-        <v>126.2</v>
+        <v>127.88</v>
       </c>
       <c r="D15" t="n">
-        <v>125.1</v>
+        <v>126.53</v>
       </c>
       <c r="E15" t="n">
-        <v>126.12</v>
+        <v>127.8</v>
       </c>
       <c r="F15" t="n">
-        <v>124.4394</v>
+        <v>124.5332</v>
       </c>
       <c r="G15" t="n">
-        <v>115.7914</v>
+        <v>115.8921</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8141,26 +7710,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>126.84</v>
+        <v>128.61</v>
       </c>
       <c r="C16" t="n">
-        <v>127.88</v>
+        <v>128.96</v>
       </c>
       <c r="D16" t="n">
-        <v>126.53</v>
+        <v>128.16</v>
       </c>
       <c r="E16" t="n">
-        <v>127.8</v>
+        <v>128.26</v>
       </c>
       <c r="F16" t="n">
-        <v>124.5332</v>
+        <v>124.6406</v>
       </c>
       <c r="G16" t="n">
-        <v>115.8921</v>
+        <v>115.9859</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8327,26 +7896,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128.61</v>
+        <v>128.24</v>
       </c>
       <c r="C17" t="n">
-        <v>128.96</v>
+        <v>128.49</v>
       </c>
       <c r="D17" t="n">
-        <v>128.16</v>
+        <v>128.02</v>
       </c>
       <c r="E17" t="n">
-        <v>128.26</v>
+        <v>128.12</v>
       </c>
       <c r="F17" t="n">
-        <v>124.6406</v>
+        <v>124.7396</v>
       </c>
       <c r="G17" t="n">
-        <v>115.9859</v>
+        <v>116.0767</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8513,26 +8082,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>128.24</v>
+        <v>128.31</v>
       </c>
       <c r="C18" t="n">
-        <v>128.49</v>
+        <v>128.72</v>
       </c>
       <c r="D18" t="n">
-        <v>128.02</v>
+        <v>128.2</v>
       </c>
       <c r="E18" t="n">
-        <v>128.12</v>
+        <v>128.65</v>
       </c>
       <c r="F18" t="n">
-        <v>124.7396</v>
+        <v>124.845</v>
       </c>
       <c r="G18" t="n">
-        <v>116.0767</v>
+        <v>116.1734</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8699,26 +8268,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>128.31</v>
+        <v>128.78</v>
       </c>
       <c r="C19" t="n">
-        <v>128.72</v>
+        <v>128.89</v>
       </c>
       <c r="D19" t="n">
-        <v>128.2</v>
+        <v>128.55</v>
       </c>
       <c r="E19" t="n">
-        <v>128.65</v>
+        <v>128.75</v>
       </c>
       <c r="F19" t="n">
-        <v>124.845</v>
+        <v>124.9454</v>
       </c>
       <c r="G19" t="n">
-        <v>116.1734</v>
+        <v>116.2684</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8885,26 +8454,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>128.78</v>
+        <v>128.8</v>
       </c>
       <c r="C20" t="n">
-        <v>128.89</v>
+        <v>129.11</v>
       </c>
       <c r="D20" t="n">
-        <v>128.55</v>
+        <v>128.7</v>
       </c>
       <c r="E20" t="n">
-        <v>128.75</v>
+        <v>128.7</v>
       </c>
       <c r="F20" t="n">
-        <v>124.9454</v>
+        <v>125.0336</v>
       </c>
       <c r="G20" t="n">
-        <v>116.2684</v>
+        <v>116.3589</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9071,26 +8640,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>129.05</v>
+      </c>
+      <c r="D21" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="E21" t="n">
         <v>128.8</v>
       </c>
-      <c r="C21" t="n">
-        <v>129.11</v>
-      </c>
-      <c r="D21" t="n">
-        <v>128.7</v>
-      </c>
-      <c r="E21" t="n">
-        <v>128.7</v>
-      </c>
       <c r="F21" t="n">
-        <v>125.0336</v>
+        <v>125.1314</v>
       </c>
       <c r="G21" t="n">
-        <v>116.3589</v>
+        <v>116.4461</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9257,26 +8826,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>128.75</v>
+        <v>129.19</v>
       </c>
       <c r="C22" t="n">
-        <v>129.05</v>
+        <v>129.83</v>
       </c>
       <c r="D22" t="n">
-        <v>128.64</v>
+        <v>129.11</v>
       </c>
       <c r="E22" t="n">
-        <v>128.8</v>
+        <v>129.39</v>
       </c>
       <c r="F22" t="n">
-        <v>125.1314</v>
+        <v>125.2418</v>
       </c>
       <c r="G22" t="n">
-        <v>116.4461</v>
+        <v>116.5352</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9443,26 +9012,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>129.19</v>
+        <v>129.51</v>
       </c>
       <c r="C23" t="n">
-        <v>129.83</v>
+        <v>129.55</v>
       </c>
       <c r="D23" t="n">
-        <v>129.11</v>
+        <v>128.84</v>
       </c>
       <c r="E23" t="n">
-        <v>129.39</v>
+        <v>128.84</v>
       </c>
       <c r="F23" t="n">
-        <v>125.2418</v>
+        <v>125.352</v>
       </c>
       <c r="G23" t="n">
-        <v>116.5352</v>
+        <v>116.6207</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9629,26 +9198,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>129.51</v>
+        <v>129.03</v>
       </c>
       <c r="C24" t="n">
-        <v>129.55</v>
+        <v>129.04</v>
       </c>
       <c r="D24" t="n">
-        <v>128.84</v>
+        <v>128.61</v>
       </c>
       <c r="E24" t="n">
-        <v>128.84</v>
+        <v>128.72</v>
       </c>
       <c r="F24" t="n">
-        <v>125.352</v>
+        <v>125.4734</v>
       </c>
       <c r="G24" t="n">
-        <v>116.6207</v>
+        <v>116.7047</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9815,26 +9384,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>129.03</v>
+        <v>127.99</v>
       </c>
       <c r="C25" t="n">
-        <v>129.04</v>
+        <v>128.06</v>
       </c>
       <c r="D25" t="n">
-        <v>128.61</v>
+        <v>127.38</v>
       </c>
       <c r="E25" t="n">
-        <v>128.72</v>
+        <v>127.42</v>
       </c>
       <c r="F25" t="n">
-        <v>125.4734</v>
+        <v>125.6048</v>
       </c>
       <c r="G25" t="n">
-        <v>116.7047</v>
+        <v>116.7829</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -10001,26 +9570,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>127.99</v>
+        <v>127.18</v>
       </c>
       <c r="C26" t="n">
-        <v>128.06</v>
+        <v>127.47</v>
       </c>
       <c r="D26" t="n">
-        <v>127.38</v>
+        <v>126.78</v>
       </c>
       <c r="E26" t="n">
-        <v>127.42</v>
+        <v>126.99</v>
       </c>
       <c r="F26" t="n">
-        <v>125.6048</v>
+        <v>125.7298</v>
       </c>
       <c r="G26" t="n">
-        <v>116.7829</v>
+        <v>116.8581</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -10187,26 +9756,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>127.18</v>
+        <v>126.71</v>
       </c>
       <c r="C27" t="n">
-        <v>127.47</v>
+        <v>126.78</v>
       </c>
       <c r="D27" t="n">
-        <v>126.78</v>
+        <v>125.8</v>
       </c>
       <c r="E27" t="n">
-        <v>126.99</v>
+        <v>126.18</v>
       </c>
       <c r="F27" t="n">
-        <v>125.7298</v>
+        <v>125.8356</v>
       </c>
       <c r="G27" t="n">
-        <v>116.8581</v>
+        <v>116.9312</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -10373,26 +9942,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>126.71</v>
+        <v>125.87</v>
       </c>
       <c r="C28" t="n">
-        <v>126.78</v>
+        <v>126.51</v>
       </c>
       <c r="D28" t="n">
-        <v>125.8</v>
+        <v>125.86</v>
       </c>
       <c r="E28" t="n">
-        <v>126.18</v>
+        <v>126.51</v>
       </c>
       <c r="F28" t="n">
-        <v>125.8356</v>
+        <v>125.9096</v>
       </c>
       <c r="G28" t="n">
-        <v>116.9312</v>
+        <v>117.0051</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -10559,26 +10128,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>125.87</v>
+        <v>126.15</v>
       </c>
       <c r="C29" t="n">
-        <v>126.51</v>
+        <v>126.5</v>
       </c>
       <c r="D29" t="n">
-        <v>125.86</v>
+        <v>125.99</v>
       </c>
       <c r="E29" t="n">
-        <v>126.51</v>
+        <v>126.23</v>
       </c>
       <c r="F29" t="n">
-        <v>125.9096</v>
+        <v>125.9494</v>
       </c>
       <c r="G29" t="n">
-        <v>117.0051</v>
+        <v>117.0851</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -10745,26 +10314,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>126.15</v>
+        <v>126.7</v>
       </c>
       <c r="C30" t="n">
-        <v>126.5</v>
+        <v>126.9</v>
       </c>
       <c r="D30" t="n">
-        <v>125.99</v>
+        <v>126.31</v>
       </c>
       <c r="E30" t="n">
-        <v>126.23</v>
+        <v>126.53</v>
       </c>
       <c r="F30" t="n">
-        <v>125.9494</v>
+        <v>125.9972</v>
       </c>
       <c r="G30" t="n">
-        <v>117.0851</v>
+        <v>117.174</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -10931,26 +10500,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>126.7</v>
+        <v>126.67</v>
       </c>
       <c r="C31" t="n">
-        <v>126.9</v>
+        <v>127.04</v>
       </c>
       <c r="D31" t="n">
-        <v>126.31</v>
+        <v>126.49</v>
       </c>
       <c r="E31" t="n">
-        <v>126.53</v>
+        <v>126.67</v>
       </c>
       <c r="F31" t="n">
-        <v>125.9972</v>
+        <v>126.0464</v>
       </c>
       <c r="G31" t="n">
-        <v>117.174</v>
+        <v>117.2526</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11117,26 +10686,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>126.67</v>
+        <v>127.06</v>
       </c>
       <c r="C32" t="n">
-        <v>127.04</v>
+        <v>127.29</v>
       </c>
       <c r="D32" t="n">
-        <v>126.49</v>
+        <v>126.78</v>
       </c>
       <c r="E32" t="n">
-        <v>126.67</v>
+        <v>127.14</v>
       </c>
       <c r="F32" t="n">
-        <v>126.0464</v>
+        <v>126.0968</v>
       </c>
       <c r="G32" t="n">
-        <v>117.2526</v>
+        <v>117.3316</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11303,26 +10872,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>127.06</v>
+        <v>127.56</v>
       </c>
       <c r="C33" t="n">
-        <v>127.29</v>
+        <v>128.28</v>
       </c>
       <c r="D33" t="n">
-        <v>126.78</v>
+        <v>127.42</v>
       </c>
       <c r="E33" t="n">
-        <v>127.14</v>
+        <v>128.22</v>
       </c>
       <c r="F33" t="n">
-        <v>126.0968</v>
+        <v>126.1648</v>
       </c>
       <c r="G33" t="n">
-        <v>117.3316</v>
+        <v>117.4129</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11489,26 +11058,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>127.56</v>
+        <v>127.59</v>
       </c>
       <c r="C34" t="n">
-        <v>128.28</v>
+        <v>127.64</v>
       </c>
       <c r="D34" t="n">
-        <v>127.42</v>
+        <v>126.77</v>
       </c>
       <c r="E34" t="n">
-        <v>128.22</v>
+        <v>126.78</v>
       </c>
       <c r="F34" t="n">
-        <v>126.1648</v>
+        <v>126.1998</v>
       </c>
       <c r="G34" t="n">
-        <v>117.4129</v>
+        <v>117.4943</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11675,26 +11244,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>127.59</v>
+        <v>127.21</v>
       </c>
       <c r="C35" t="n">
-        <v>127.64</v>
+        <v>127.35</v>
       </c>
       <c r="D35" t="n">
-        <v>126.77</v>
+        <v>126.26</v>
       </c>
       <c r="E35" t="n">
-        <v>126.78</v>
+        <v>126.58</v>
       </c>
       <c r="F35" t="n">
-        <v>126.1998</v>
+        <v>126.2516</v>
       </c>
       <c r="G35" t="n">
-        <v>117.4943</v>
+        <v>117.5762</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11861,26 +11430,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>127.21</v>
+        <v>126.5</v>
       </c>
       <c r="C36" t="n">
-        <v>127.35</v>
+        <v>126.91</v>
       </c>
       <c r="D36" t="n">
-        <v>126.26</v>
+        <v>125.92</v>
       </c>
       <c r="E36" t="n">
-        <v>126.58</v>
+        <v>126.79</v>
       </c>
       <c r="F36" t="n">
-        <v>126.2516</v>
+        <v>126.2926</v>
       </c>
       <c r="G36" t="n">
-        <v>117.5762</v>
+        <v>117.6614</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12047,26 +11616,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>126.5</v>
+        <v>126.81</v>
       </c>
       <c r="C37" t="n">
-        <v>126.91</v>
+        <v>127.88</v>
       </c>
       <c r="D37" t="n">
-        <v>125.92</v>
+        <v>126.71</v>
       </c>
       <c r="E37" t="n">
-        <v>126.79</v>
+        <v>127.88</v>
       </c>
       <c r="F37" t="n">
-        <v>126.2926</v>
+        <v>126.3684</v>
       </c>
       <c r="G37" t="n">
-        <v>117.6614</v>
+        <v>117.7593</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -12233,26 +11802,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>126.81</v>
+        <v>127.75</v>
       </c>
       <c r="C38" t="n">
-        <v>127.88</v>
+        <v>128.09</v>
       </c>
       <c r="D38" t="n">
-        <v>126.71</v>
+        <v>127</v>
       </c>
       <c r="E38" t="n">
-        <v>127.88</v>
+        <v>127.44</v>
       </c>
       <c r="F38" t="n">
-        <v>126.3684</v>
+        <v>126.4426</v>
       </c>
       <c r="G38" t="n">
-        <v>117.7593</v>
+        <v>117.8536</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -12419,26 +11988,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>127.75</v>
+        <v>127.66</v>
       </c>
       <c r="C39" t="n">
-        <v>128.09</v>
+        <v>127.7</v>
       </c>
       <c r="D39" t="n">
-        <v>127</v>
+        <v>127.27</v>
       </c>
       <c r="E39" t="n">
-        <v>127.44</v>
+        <v>127.33</v>
       </c>
       <c r="F39" t="n">
-        <v>126.4426</v>
+        <v>126.5118</v>
       </c>
       <c r="G39" t="n">
-        <v>117.8536</v>
+        <v>117.9441</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12605,26 +12174,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>127.66</v>
+        <v>127.25</v>
       </c>
       <c r="C40" t="n">
-        <v>127.7</v>
+        <v>127.5</v>
       </c>
       <c r="D40" t="n">
-        <v>127.27</v>
+        <v>126.95</v>
       </c>
       <c r="E40" t="n">
-        <v>127.33</v>
+        <v>127.16</v>
       </c>
       <c r="F40" t="n">
-        <v>126.5118</v>
+        <v>126.5524</v>
       </c>
       <c r="G40" t="n">
-        <v>117.9441</v>
+        <v>118.0394</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12791,26 +12360,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>127.25</v>
+        <v>126.85</v>
       </c>
       <c r="C41" t="n">
-        <v>127.5</v>
+        <v>126.93</v>
       </c>
       <c r="D41" t="n">
-        <v>126.95</v>
+        <v>125.85</v>
       </c>
       <c r="E41" t="n">
-        <v>127.16</v>
+        <v>126.05</v>
       </c>
       <c r="F41" t="n">
-        <v>126.5524</v>
+        <v>126.5562</v>
       </c>
       <c r="G41" t="n">
-        <v>118.0394</v>
+        <v>118.122</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12977,26 +12546,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>126.85</v>
+        <v>126.31</v>
       </c>
       <c r="C42" t="n">
-        <v>126.93</v>
+        <v>126.35</v>
       </c>
       <c r="D42" t="n">
-        <v>125.85</v>
+        <v>125.17</v>
       </c>
       <c r="E42" t="n">
-        <v>126.05</v>
+        <v>125.44</v>
       </c>
       <c r="F42" t="n">
-        <v>126.5562</v>
+        <v>126.5604</v>
       </c>
       <c r="G42" t="n">
-        <v>118.122</v>
+        <v>118.2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -13163,26 +12732,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>126.31</v>
+        <v>125.94</v>
       </c>
       <c r="C43" t="n">
-        <v>126.35</v>
+        <v>126.81</v>
       </c>
       <c r="D43" t="n">
-        <v>125.17</v>
+        <v>125.8</v>
       </c>
       <c r="E43" t="n">
-        <v>125.44</v>
+        <v>126.64</v>
       </c>
       <c r="F43" t="n">
-        <v>126.5604</v>
+        <v>126.5784</v>
       </c>
       <c r="G43" t="n">
-        <v>118.2</v>
+        <v>118.2779</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -13349,26 +12918,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>125.94</v>
+        <v>126.14</v>
       </c>
       <c r="C44" t="n">
-        <v>126.81</v>
+        <v>126.57</v>
       </c>
       <c r="D44" t="n">
-        <v>125.8</v>
+        <v>125.98</v>
       </c>
       <c r="E44" t="n">
-        <v>126.64</v>
+        <v>126.43</v>
       </c>
       <c r="F44" t="n">
-        <v>126.5784</v>
+        <v>126.58</v>
       </c>
       <c r="G44" t="n">
-        <v>118.2779</v>
+        <v>118.3551</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -13535,26 +13104,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>126.14</v>
+        <v>126.03</v>
       </c>
       <c r="C45" t="n">
-        <v>126.57</v>
+        <v>126.34</v>
       </c>
       <c r="D45" t="n">
-        <v>125.98</v>
+        <v>125.52</v>
       </c>
       <c r="E45" t="n">
-        <v>126.43</v>
+        <v>125.81</v>
       </c>
       <c r="F45" t="n">
-        <v>126.58</v>
+        <v>126.5882</v>
       </c>
       <c r="G45" t="n">
-        <v>118.3551</v>
+        <v>118.4271</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -13623,7 +13192,7 @@
         <v>1502.867</v>
       </c>
       <c r="AE45" t="n">
-        <v>1301.1272</v>
+        <v>1301.1271</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -13721,26 +13290,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>126.03</v>
+        <v>126.18</v>
       </c>
       <c r="C46" t="n">
-        <v>126.34</v>
+        <v>126.55</v>
       </c>
       <c r="D46" t="n">
-        <v>125.52</v>
+        <v>125.97</v>
       </c>
       <c r="E46" t="n">
-        <v>125.81</v>
+        <v>126.47</v>
       </c>
       <c r="F46" t="n">
-        <v>126.5882</v>
+        <v>126.6282</v>
       </c>
       <c r="G46" t="n">
-        <v>118.4271</v>
+        <v>118.5046</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -13907,26 +13476,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>126.18</v>
+        <v>127.05</v>
       </c>
       <c r="C47" t="n">
-        <v>126.55</v>
+        <v>127.65</v>
       </c>
       <c r="D47" t="n">
-        <v>125.97</v>
+        <v>126.94</v>
       </c>
       <c r="E47" t="n">
-        <v>126.47</v>
+        <v>127.4</v>
       </c>
       <c r="F47" t="n">
-        <v>126.6282</v>
+        <v>126.6618</v>
       </c>
       <c r="G47" t="n">
-        <v>118.5046</v>
+        <v>118.5867</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -14093,26 +13662,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>127.69</v>
+      </c>
+      <c r="C48" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="D48" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="E48" t="n">
         <v>127.05</v>
       </c>
-      <c r="C48" t="n">
-        <v>127.65</v>
-      </c>
-      <c r="D48" t="n">
-        <v>126.94</v>
-      </c>
-      <c r="E48" t="n">
-        <v>127.4</v>
-      </c>
       <c r="F48" t="n">
-        <v>126.6618</v>
+        <v>126.6798</v>
       </c>
       <c r="G48" t="n">
-        <v>118.5867</v>
+        <v>118.6667</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -14279,26 +13848,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>127.69</v>
+        <v>127.98</v>
       </c>
       <c r="C49" t="n">
-        <v>127.78</v>
+        <v>128.65</v>
       </c>
       <c r="D49" t="n">
-        <v>126.9</v>
+        <v>127.89</v>
       </c>
       <c r="E49" t="n">
-        <v>127.05</v>
+        <v>128.62</v>
       </c>
       <c r="F49" t="n">
-        <v>126.6798</v>
+        <v>126.7256</v>
       </c>
       <c r="G49" t="n">
-        <v>118.6667</v>
+        <v>118.7534</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -14465,26 +14034,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>127.98</v>
+        <v>129.21</v>
       </c>
       <c r="C50" t="n">
-        <v>128.65</v>
+        <v>129.55</v>
       </c>
       <c r="D50" t="n">
-        <v>127.89</v>
+        <v>129</v>
       </c>
       <c r="E50" t="n">
-        <v>128.62</v>
+        <v>129.38</v>
       </c>
       <c r="F50" t="n">
-        <v>126.7256</v>
+        <v>126.7914</v>
       </c>
       <c r="G50" t="n">
-        <v>118.7534</v>
+        <v>118.8419</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -14651,26 +14220,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>129.21</v>
+        <v>129.76</v>
       </c>
       <c r="C51" t="n">
-        <v>129.55</v>
+        <v>129.83</v>
       </c>
       <c r="D51" t="n">
-        <v>129</v>
+        <v>129.04</v>
       </c>
       <c r="E51" t="n">
-        <v>129.38</v>
+        <v>129.1</v>
       </c>
       <c r="F51" t="n">
-        <v>126.7914</v>
+        <v>126.8476</v>
       </c>
       <c r="G51" t="n">
-        <v>118.8419</v>
+        <v>118.9298</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -14837,26 +14406,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>129.76</v>
+        <v>128.26</v>
       </c>
       <c r="C52" t="n">
-        <v>129.83</v>
+        <v>128.77</v>
       </c>
       <c r="D52" t="n">
-        <v>129.04</v>
+        <v>128.03</v>
       </c>
       <c r="E52" t="n">
-        <v>129.1</v>
+        <v>128.37</v>
       </c>
       <c r="F52" t="n">
-        <v>126.8476</v>
+        <v>126.8898</v>
       </c>
       <c r="G52" t="n">
-        <v>118.9298</v>
+        <v>119.0135</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -15023,26 +14592,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>128.26</v>
+        <v>129.11</v>
       </c>
       <c r="C53" t="n">
-        <v>128.77</v>
+        <v>129.3</v>
       </c>
       <c r="D53" t="n">
-        <v>128.03</v>
+        <v>128.49</v>
       </c>
       <c r="E53" t="n">
-        <v>128.37</v>
+        <v>128.91</v>
       </c>
       <c r="F53" t="n">
-        <v>126.8898</v>
+        <v>126.971</v>
       </c>
       <c r="G53" t="n">
-        <v>119.0135</v>
+        <v>119.1011</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -15209,26 +14778,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>129.11</v>
+        <v>129.02</v>
       </c>
       <c r="C54" t="n">
-        <v>129.3</v>
+        <v>129.26</v>
       </c>
       <c r="D54" t="n">
-        <v>128.49</v>
+        <v>128.54</v>
       </c>
       <c r="E54" t="n">
-        <v>128.91</v>
+        <v>128.57</v>
       </c>
       <c r="F54" t="n">
-        <v>126.971</v>
+        <v>127.0372</v>
       </c>
       <c r="G54" t="n">
-        <v>119.1011</v>
+        <v>119.1891</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -15395,26 +14964,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>129.02</v>
+        <v>128.72</v>
       </c>
       <c r="C55" t="n">
-        <v>129.26</v>
+        <v>129.27</v>
       </c>
       <c r="D55" t="n">
-        <v>128.54</v>
+        <v>128.55</v>
       </c>
       <c r="E55" t="n">
-        <v>128.57</v>
+        <v>128.7</v>
       </c>
       <c r="F55" t="n">
-        <v>127.0372</v>
+        <v>127.0962</v>
       </c>
       <c r="G55" t="n">
-        <v>119.1891</v>
+        <v>119.2811</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -15581,26 +15150,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>128.72</v>
+        <v>129.08</v>
       </c>
       <c r="C56" t="n">
-        <v>129.27</v>
+        <v>129.4</v>
       </c>
       <c r="D56" t="n">
-        <v>128.55</v>
+        <v>128.57</v>
       </c>
       <c r="E56" t="n">
-        <v>128.7</v>
+        <v>129.15</v>
       </c>
       <c r="F56" t="n">
-        <v>127.0962</v>
+        <v>127.1586</v>
       </c>
       <c r="G56" t="n">
-        <v>119.2811</v>
+        <v>119.3744</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -15669,7 +15238,7 @@
         <v>1490.0724</v>
       </c>
       <c r="AE56" t="n">
-        <v>1332.1048</v>
+        <v>1332.1047</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -15767,26 +15336,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>129.08</v>
+        <v>129.07</v>
       </c>
       <c r="C57" t="n">
         <v>129.4</v>
       </c>
       <c r="D57" t="n">
-        <v>128.57</v>
+        <v>128.31</v>
       </c>
       <c r="E57" t="n">
-        <v>129.15</v>
+        <v>128.81</v>
       </c>
       <c r="F57" t="n">
-        <v>127.1586</v>
+        <v>127.2468</v>
       </c>
       <c r="G57" t="n">
-        <v>119.3744</v>
+        <v>119.4698</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -15953,26 +15522,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>129.07</v>
+        <v>129.53</v>
       </c>
       <c r="C58" t="n">
-        <v>129.4</v>
+        <v>130.55</v>
       </c>
       <c r="D58" t="n">
-        <v>128.31</v>
+        <v>129.43</v>
       </c>
       <c r="E58" t="n">
-        <v>128.81</v>
+        <v>130.05</v>
       </c>
       <c r="F58" t="n">
-        <v>127.2468</v>
+        <v>127.3426</v>
       </c>
       <c r="G58" t="n">
-        <v>119.4698</v>
+        <v>119.5736</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -16139,26 +15708,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>129.53</v>
+        <v>130.86</v>
       </c>
       <c r="C59" t="n">
-        <v>130.55</v>
+        <v>131.42</v>
       </c>
       <c r="D59" t="n">
-        <v>129.43</v>
+        <v>130.48</v>
       </c>
       <c r="E59" t="n">
-        <v>130.05</v>
+        <v>131.18</v>
       </c>
       <c r="F59" t="n">
-        <v>127.3426</v>
+        <v>127.4712</v>
       </c>
       <c r="G59" t="n">
-        <v>119.5736</v>
+        <v>119.6774</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -16325,26 +15894,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>130.86</v>
+        <v>131.69</v>
       </c>
       <c r="C60" t="n">
-        <v>131.42</v>
+        <v>131.94</v>
       </c>
       <c r="D60" t="n">
-        <v>130.48</v>
+        <v>131.41</v>
       </c>
       <c r="E60" t="n">
-        <v>131.18</v>
+        <v>131.87</v>
       </c>
       <c r="F60" t="n">
-        <v>127.4712</v>
+        <v>127.605</v>
       </c>
       <c r="G60" t="n">
-        <v>119.6774</v>
+        <v>119.782</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -16511,26 +16080,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>131.69</v>
+        <v>131.82</v>
       </c>
       <c r="C61" t="n">
-        <v>131.94</v>
+        <v>132.32</v>
       </c>
       <c r="D61" t="n">
-        <v>131.41</v>
+        <v>131.18</v>
       </c>
       <c r="E61" t="n">
-        <v>131.87</v>
+        <v>131.45</v>
       </c>
       <c r="F61" t="n">
-        <v>127.605</v>
+        <v>127.7474</v>
       </c>
       <c r="G61" t="n">
-        <v>119.782</v>
+        <v>119.8834</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -16697,26 +16266,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>131.82</v>
+        <v>130.99</v>
       </c>
       <c r="C62" t="n">
-        <v>132.32</v>
+        <v>131.39</v>
       </c>
       <c r="D62" t="n">
-        <v>131.18</v>
+        <v>130.81</v>
       </c>
       <c r="E62" t="n">
-        <v>131.45</v>
+        <v>130.98</v>
       </c>
       <c r="F62" t="n">
-        <v>127.7474</v>
+        <v>127.8932</v>
       </c>
       <c r="G62" t="n">
-        <v>119.8834</v>
+        <v>119.9813</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -16883,26 +16452,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>130.99</v>
+        <v>131.19</v>
       </c>
       <c r="C63" t="n">
-        <v>131.39</v>
+        <v>131.73</v>
       </c>
       <c r="D63" t="n">
-        <v>130.81</v>
+        <v>131.14</v>
       </c>
       <c r="E63" t="n">
-        <v>130.98</v>
+        <v>131.67</v>
       </c>
       <c r="F63" t="n">
-        <v>127.8932</v>
+        <v>128.042</v>
       </c>
       <c r="G63" t="n">
-        <v>119.9813</v>
+        <v>120.0822</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -17069,26 +16638,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>131.19</v>
+        <v>132.12</v>
       </c>
       <c r="C64" t="n">
-        <v>131.73</v>
+        <v>132.32</v>
       </c>
       <c r="D64" t="n">
-        <v>131.14</v>
+        <v>132.04</v>
       </c>
       <c r="E64" t="n">
-        <v>131.67</v>
+        <v>132.26</v>
       </c>
       <c r="F64" t="n">
-        <v>128.042</v>
+        <v>128.1648</v>
       </c>
       <c r="G64" t="n">
-        <v>120.0822</v>
+        <v>120.1856</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -17255,26 +16824,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>132.12</v>
+        <v>132.04</v>
       </c>
       <c r="C65" t="n">
-        <v>132.32</v>
+        <v>132.4</v>
       </c>
       <c r="D65" t="n">
-        <v>132.04</v>
+        <v>131.71</v>
       </c>
       <c r="E65" t="n">
-        <v>132.26</v>
+        <v>131.73</v>
       </c>
       <c r="F65" t="n">
-        <v>128.1648</v>
+        <v>128.2434</v>
       </c>
       <c r="G65" t="n">
-        <v>120.1856</v>
+        <v>120.2853</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -17457,10 +17026,10 @@
         <v>131.81</v>
       </c>
       <c r="F66" t="n">
-        <v>128.245</v>
+        <v>128.3144</v>
       </c>
       <c r="G66" t="n">
-        <v>120.2857</v>
+        <v>120.3867</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -17474,7 +17043,7 @@
         <v>949.42</v>
       </c>
       <c r="L66" t="n">
-        <v>913.65</v>
+        <v>913.6</v>
       </c>
       <c r="M66" t="n">
         <v>914.13</v>
@@ -17592,13 +17161,13 @@
         <v>2408.7908</v>
       </c>
       <c r="BA66" t="n">
-        <v>2423.8</v>
+        <v>2422.78</v>
       </c>
       <c r="BB66" t="n">
-        <v>2555.6857</v>
+        <v>2555.6653</v>
       </c>
       <c r="BC66" t="n">
-        <v>2140.4752</v>
+        <v>2140.4701</v>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -17615,13 +17184,13 @@
         <v>81469.35159999999</v>
       </c>
       <c r="BI66" t="n">
-        <v>81822.75780000001</v>
+        <v>81779.10159999999</v>
       </c>
       <c r="BJ66" t="n">
-        <v>81169.9184</v>
+        <v>81169.0453</v>
       </c>
       <c r="BK66" t="n">
-        <v>72206.2684</v>
+        <v>72206.0502</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/voorbeeld/investeerder.xlsx
+++ b/rapporten/voorbeeld/investeerder.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9820.690000000001</v>
+        <v>9803.33</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -4046,7 +4046,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>iShares MSCI World (IWDA.AS)  ·  131,81 EUR</t>
+          <t>iShares MSCI World (IWDA.AS)  ·  131,78 EUR</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -4118,24 +4118,24 @@
     <row r="69" ht="22" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Ethereum (ETH-USD)  ·  2.422,78 USD</t>
+          <t>Ethereum (ETH-USD)  ·  2.418,21 USD</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Bitcoin (BTC-USD)  ·  81.779,10 USD</t>
+          <t>Bitcoin (BTC-USD)  ·  81.562,49 USD</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Gestegen: 28,8% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gestegen: 28,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Gestegen: 28,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+          <t>Gestegen: 28,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.611</v>
+        <v>0.6119</v>
       </c>
     </row>
     <row r="3">
@@ -4220,43 +4220,43 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.0587</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Halfgeleider-ETF</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>STOCK</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0584</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Halfgeleider-ETF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>STOCK</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0573</v>
+        <v>0.0574</v>
       </c>
     </row>
     <row r="7">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0565</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="8">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0503</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0497</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="10">
@@ -5133,22 +5133,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>975.8099999999999</v>
+        <v>975.6565000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>978.4</v>
+        <v>978.2461</v>
       </c>
       <c r="L2" t="n">
-        <v>873.63</v>
+        <v>873.4926</v>
       </c>
       <c r="M2" t="n">
-        <v>904.28</v>
+        <v>904.1378</v>
       </c>
       <c r="N2" t="n">
-        <v>923.8603000000001</v>
+        <v>923.7148999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>476.0013</v>
+        <v>475.9264</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -5319,22 +5319,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>866.77</v>
+        <v>866.6336</v>
       </c>
       <c r="K3" t="n">
-        <v>887.71</v>
+        <v>887.5703</v>
       </c>
       <c r="L3" t="n">
-        <v>840.51</v>
+        <v>840.3777</v>
       </c>
       <c r="M3" t="n">
-        <v>853.2</v>
+        <v>853.0657</v>
       </c>
       <c r="N3" t="n">
-        <v>929.3971</v>
+        <v>929.2508</v>
       </c>
       <c r="O3" t="n">
-        <v>479.4822</v>
+        <v>479.4068</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -5505,22 +5505,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>822.53</v>
+        <v>822.4006000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>903.96</v>
+        <v>903.8178</v>
       </c>
       <c r="L4" t="n">
-        <v>804</v>
+        <v>803.8735</v>
       </c>
       <c r="M4" t="n">
-        <v>848.95</v>
+        <v>848.8164</v>
       </c>
       <c r="N4" t="n">
-        <v>933.574</v>
+        <v>933.4271</v>
       </c>
       <c r="O4" t="n">
-        <v>482.9088</v>
+        <v>482.8328</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -5691,22 +5691,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>885.5700000000001</v>
+        <v>885.4307</v>
       </c>
       <c r="K5" t="n">
-        <v>901</v>
+        <v>900.8582</v>
       </c>
       <c r="L5" t="n">
-        <v>858.9</v>
+        <v>858.7649</v>
       </c>
       <c r="M5" t="n">
-        <v>865.46</v>
+        <v>865.3239</v>
       </c>
       <c r="N5" t="n">
-        <v>937.5535</v>
+        <v>937.4059999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>486.4008</v>
+        <v>486.3243</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -5877,22 +5877,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>925.35</v>
+        <v>925.2044</v>
       </c>
       <c r="K6" t="n">
-        <v>982.88</v>
+        <v>982.7252999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>916.5700000000001</v>
+        <v>916.4258</v>
       </c>
       <c r="M6" t="n">
-        <v>970.8200000000001</v>
+        <v>970.6672</v>
       </c>
       <c r="N6" t="n">
-        <v>944.0393</v>
+        <v>943.8907</v>
       </c>
       <c r="O6" t="n">
-        <v>490.3456</v>
+        <v>490.2685</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -6063,22 +6063,22 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>938.25</v>
+        <v>938.1023</v>
       </c>
       <c r="K7" t="n">
-        <v>982.62</v>
+        <v>982.4654</v>
       </c>
       <c r="L7" t="n">
-        <v>936.0599999999999</v>
+        <v>935.9127</v>
       </c>
       <c r="M7" t="n">
-        <v>959.48</v>
+        <v>959.329</v>
       </c>
       <c r="N7" t="n">
-        <v>948.295</v>
+        <v>948.1458</v>
       </c>
       <c r="O7" t="n">
-        <v>494.2258</v>
+        <v>494.148</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -6249,22 +6249,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>975.13</v>
+        <v>974.9766</v>
       </c>
       <c r="K8" t="n">
-        <v>1011.77</v>
+        <v>1011.6108</v>
       </c>
       <c r="L8" t="n">
-        <v>964.4</v>
+        <v>964.2483</v>
       </c>
       <c r="M8" t="n">
-        <v>990.21</v>
+        <v>990.0542</v>
       </c>
       <c r="N8" t="n">
-        <v>952.1950000000001</v>
+        <v>952.0452</v>
       </c>
       <c r="O8" t="n">
-        <v>498.2386</v>
+        <v>498.1602</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -6435,22 +6435,22 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>959.03</v>
+        <v>958.8791</v>
       </c>
       <c r="K9" t="n">
-        <v>967.14</v>
+        <v>966.9878</v>
       </c>
       <c r="L9" t="n">
-        <v>904</v>
+        <v>903.8578</v>
       </c>
       <c r="M9" t="n">
-        <v>920.95</v>
+        <v>920.8051</v>
       </c>
       <c r="N9" t="n">
-        <v>955.2848</v>
+        <v>955.1345</v>
       </c>
       <c r="O9" t="n">
-        <v>501.8895</v>
+        <v>501.8105</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -6621,22 +6621,22 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>932.45</v>
+        <v>932.3033</v>
       </c>
       <c r="K10" t="n">
-        <v>935</v>
+        <v>934.8529</v>
       </c>
       <c r="L10" t="n">
-        <v>854.79</v>
+        <v>854.6555</v>
       </c>
       <c r="M10" t="n">
-        <v>900.2</v>
+        <v>900.0583</v>
       </c>
       <c r="N10" t="n">
-        <v>957.2186</v>
+        <v>957.068</v>
       </c>
       <c r="O10" t="n">
-        <v>505.4629</v>
+        <v>505.3834</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -6807,22 +6807,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>839.61</v>
+        <v>839.4779</v>
       </c>
       <c r="K11" t="n">
-        <v>848.36</v>
+        <v>848.2265</v>
       </c>
       <c r="L11" t="n">
-        <v>789.09</v>
+        <v>788.9659</v>
       </c>
       <c r="M11" t="n">
-        <v>820.53</v>
+        <v>820.4009</v>
       </c>
       <c r="N11" t="n">
-        <v>958.1114</v>
+        <v>957.9607</v>
       </c>
       <c r="O11" t="n">
-        <v>508.5838</v>
+        <v>508.5038</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -6993,22 +6993,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>833</v>
+        <v>832.8689000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>841.8</v>
+        <v>841.6675</v>
       </c>
       <c r="L12" t="n">
-        <v>737.88</v>
+        <v>737.7639</v>
       </c>
       <c r="M12" t="n">
-        <v>739</v>
+        <v>738.8837</v>
       </c>
       <c r="N12" t="n">
-        <v>958.4005</v>
+        <v>958.2497</v>
       </c>
       <c r="O12" t="n">
-        <v>511.3181</v>
+        <v>511.2377</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>1535.0628</v>
       </c>
       <c r="AE12" t="n">
-        <v>1201.4256</v>
+        <v>1201.4255</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -7179,22 +7179,22 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>793.14</v>
+        <v>793.0152</v>
       </c>
       <c r="K13" t="n">
-        <v>882.5</v>
+        <v>882.3611</v>
       </c>
       <c r="L13" t="n">
-        <v>789</v>
+        <v>788.8758</v>
       </c>
       <c r="M13" t="n">
-        <v>874.66</v>
+        <v>874.5223</v>
       </c>
       <c r="N13" t="n">
-        <v>962.265</v>
+        <v>962.1135</v>
       </c>
       <c r="O13" t="n">
-        <v>514.7843</v>
+        <v>514.7033</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -7365,22 +7365,22 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>919.65</v>
+        <v>919.5053</v>
       </c>
       <c r="K14" t="n">
-        <v>930.88</v>
+        <v>930.7335</v>
       </c>
       <c r="L14" t="n">
-        <v>818</v>
+        <v>817.8713</v>
       </c>
       <c r="M14" t="n">
-        <v>823.03</v>
+        <v>822.9005</v>
       </c>
       <c r="N14" t="n">
-        <v>964.7529</v>
+        <v>964.6011</v>
       </c>
       <c r="O14" t="n">
-        <v>517.9365</v>
+        <v>517.855</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -7551,22 +7551,22 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>786.36</v>
+        <v>786.2362000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>836.62</v>
+        <v>836.4883</v>
       </c>
       <c r="L15" t="n">
-        <v>770.1</v>
+        <v>769.9788</v>
       </c>
       <c r="M15" t="n">
-        <v>829.5</v>
+        <v>829.3694</v>
       </c>
       <c r="N15" t="n">
-        <v>966.7054000000001</v>
+        <v>966.5531999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>521.1497000000001</v>
+        <v>521.0676999999999</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -7737,22 +7737,22 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>866.8200000000001</v>
+        <v>866.6836</v>
       </c>
       <c r="K16" t="n">
-        <v>902.4299999999999</v>
+        <v>902.288</v>
       </c>
       <c r="L16" t="n">
-        <v>858.5</v>
+        <v>858.3649</v>
       </c>
       <c r="M16" t="n">
-        <v>892.67</v>
+        <v>892.5295</v>
       </c>
       <c r="N16" t="n">
-        <v>969.3191</v>
+        <v>969.1666</v>
       </c>
       <c r="O16" t="n">
-        <v>524.6541999999999</v>
+        <v>524.5717</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -7923,22 +7923,22 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>885.3</v>
+        <v>885.1607</v>
       </c>
       <c r="K17" t="n">
-        <v>928.98</v>
+        <v>928.8338</v>
       </c>
       <c r="L17" t="n">
-        <v>881.2</v>
+        <v>881.0613</v>
       </c>
       <c r="M17" t="n">
-        <v>893.1900000000001</v>
+        <v>893.0494</v>
       </c>
       <c r="N17" t="n">
-        <v>972.1652</v>
+        <v>972.0122</v>
       </c>
       <c r="O17" t="n">
-        <v>528.1085</v>
+        <v>528.0254</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -8109,22 +8109,22 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>843.11</v>
+        <v>842.9773</v>
       </c>
       <c r="K18" t="n">
-        <v>913.33</v>
+        <v>913.1863</v>
       </c>
       <c r="L18" t="n">
-        <v>827</v>
+        <v>826.8698000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>881.47</v>
+        <v>881.3312</v>
       </c>
       <c r="N18" t="n">
-        <v>971.8798</v>
+        <v>971.7268</v>
       </c>
       <c r="O18" t="n">
-        <v>531.505</v>
+        <v>531.4213</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -8295,22 +8295,22 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>903.6</v>
+        <v>903.4578</v>
       </c>
       <c r="K19" t="n">
-        <v>904.8</v>
+        <v>904.6576</v>
       </c>
       <c r="L19" t="n">
-        <v>847.02</v>
+        <v>846.8868</v>
       </c>
       <c r="M19" t="n">
-        <v>877.5700000000001</v>
+        <v>877.4319</v>
       </c>
       <c r="N19" t="n">
-        <v>970.8658</v>
+        <v>970.7131000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>534.86</v>
+        <v>534.7758</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -8481,22 +8481,22 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>863.67</v>
+        <v>863.5341</v>
       </c>
       <c r="K20" t="n">
-        <v>894.99</v>
+        <v>894.8491</v>
       </c>
       <c r="L20" t="n">
-        <v>854.4</v>
+        <v>854.2655999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>861</v>
+        <v>860.8645</v>
       </c>
       <c r="N20" t="n">
-        <v>969.6183</v>
+        <v>969.4657</v>
       </c>
       <c r="O20" t="n">
-        <v>538.1545</v>
+        <v>538.0698</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -8667,22 +8667,22 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>871.8</v>
+        <v>871.6627999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>879</v>
+        <v>878.8617</v>
       </c>
       <c r="L21" t="n">
-        <v>844.62</v>
+        <v>844.4871000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>868.52</v>
+        <v>868.3834000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>967.5717</v>
+        <v>967.4194</v>
       </c>
       <c r="O21" t="n">
-        <v>541.5057</v>
+        <v>541.4204999999999</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -8853,22 +8853,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>912.9400000000001</v>
+        <v>912.7963999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>935.8</v>
+        <v>935.6528</v>
       </c>
       <c r="L22" t="n">
-        <v>899.54</v>
+        <v>899.3985</v>
       </c>
       <c r="M22" t="n">
-        <v>911.29</v>
+        <v>911.1466</v>
       </c>
       <c r="N22" t="n">
-        <v>965.0906</v>
+        <v>964.9388</v>
       </c>
       <c r="O22" t="n">
-        <v>545.0297</v>
+        <v>544.9439</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -9039,22 +9039,22 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>912.89</v>
+        <v>912.7464</v>
       </c>
       <c r="K23" t="n">
-        <v>978</v>
+        <v>977.8461</v>
       </c>
       <c r="L23" t="n">
-        <v>906.5</v>
+        <v>906.3573</v>
       </c>
       <c r="M23" t="n">
-        <v>949.83</v>
+        <v>949.6805000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>962.8085</v>
+        <v>962.657</v>
       </c>
       <c r="O23" t="n">
-        <v>548.6848</v>
+        <v>548.5984</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -9225,22 +9225,22 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>979.3200000000001</v>
+        <v>979.1659</v>
       </c>
       <c r="K24" t="n">
-        <v>984</v>
+        <v>983.8452</v>
       </c>
       <c r="L24" t="n">
-        <v>956.2</v>
+        <v>956.0496000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>971.66</v>
+        <v>971.5071</v>
       </c>
       <c r="N24" t="n">
-        <v>960.6536</v>
+        <v>960.5025000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>552.4435999999999</v>
+        <v>552.3567</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -9411,22 +9411,22 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>999.55</v>
+        <v>999.3927</v>
       </c>
       <c r="K25" t="n">
-        <v>1036.13</v>
+        <v>1035.967</v>
       </c>
       <c r="L25" t="n">
-        <v>995.26</v>
+        <v>995.1034</v>
       </c>
       <c r="M25" t="n">
-        <v>1011.75</v>
+        <v>1011.5908</v>
       </c>
       <c r="N25" t="n">
-        <v>960.9717000000001</v>
+        <v>960.8205</v>
       </c>
       <c r="O25" t="n">
-        <v>556.3939</v>
+        <v>556.3064000000001</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -9597,22 +9597,22 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>957.1</v>
+        <v>956.9494</v>
       </c>
       <c r="K26" t="n">
-        <v>978.67</v>
+        <v>978.516</v>
       </c>
       <c r="L26" t="n">
-        <v>926.64</v>
+        <v>926.4942</v>
       </c>
       <c r="M26" t="n">
-        <v>940.76</v>
+        <v>940.612</v>
       </c>
       <c r="N26" t="n">
-        <v>962.5094</v>
+        <v>962.3579</v>
       </c>
       <c r="O26" t="n">
-        <v>559.9657</v>
+        <v>559.8776</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -9783,22 +9783,22 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>959.36</v>
+        <v>959.2089999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>960</v>
+        <v>959.8489</v>
       </c>
       <c r="L27" t="n">
-        <v>915.1799999999999</v>
+        <v>915.0359999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>937.11</v>
+        <v>936.9625</v>
       </c>
       <c r="N27" t="n">
-        <v>962.2689</v>
+        <v>962.1174999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>563.5323</v>
+        <v>563.4435999999999</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -9969,22 +9969,22 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>935.01</v>
+        <v>934.8629</v>
       </c>
       <c r="K28" t="n">
-        <v>977.28</v>
+        <v>977.1262</v>
       </c>
       <c r="L28" t="n">
-        <v>929.0700000000001</v>
+        <v>928.9238</v>
       </c>
       <c r="M28" t="n">
-        <v>974.33</v>
+        <v>974.1767</v>
       </c>
       <c r="N28" t="n">
-        <v>963.0405</v>
+        <v>962.889</v>
       </c>
       <c r="O28" t="n">
-        <v>567.2862</v>
+        <v>567.1969</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -10155,22 +10155,22 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>989.6799999999999</v>
+        <v>989.5243</v>
       </c>
       <c r="K29" t="n">
-        <v>989.96</v>
+        <v>989.8043</v>
       </c>
       <c r="L29" t="n">
-        <v>958.26</v>
+        <v>958.1093</v>
       </c>
       <c r="M29" t="n">
-        <v>966.78</v>
+        <v>966.6279</v>
       </c>
       <c r="N29" t="n">
-        <v>964.5413</v>
+        <v>964.3895</v>
       </c>
       <c r="O29" t="n">
-        <v>570.9477000000001</v>
+        <v>570.8579</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -10341,22 +10341,22 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>934.78</v>
+        <v>934.6328999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>936.45</v>
+        <v>936.3027</v>
       </c>
       <c r="L30" t="n">
-        <v>887.61</v>
+        <v>887.4703</v>
       </c>
       <c r="M30" t="n">
-        <v>910.4299999999999</v>
+        <v>910.2867</v>
       </c>
       <c r="N30" t="n">
-        <v>962.8356</v>
+        <v>962.684</v>
       </c>
       <c r="O30" t="n">
-        <v>574.4108</v>
+        <v>574.3203999999999</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -10527,22 +10527,22 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>928.98</v>
+        <v>928.8338</v>
       </c>
       <c r="K31" t="n">
-        <v>946.67</v>
+        <v>946.521</v>
       </c>
       <c r="L31" t="n">
-        <v>916.3</v>
+        <v>916.1558</v>
       </c>
       <c r="M31" t="n">
-        <v>932.97</v>
+        <v>932.8232</v>
       </c>
       <c r="N31" t="n">
-        <v>961.8658</v>
+        <v>961.7144</v>
       </c>
       <c r="O31" t="n">
-        <v>577.8893</v>
+        <v>577.7984</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -10713,22 +10713,22 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>925.74</v>
+        <v>925.5943</v>
       </c>
       <c r="K32" t="n">
-        <v>945.75</v>
+        <v>945.6011999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>924.6</v>
+        <v>924.4545000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>938.4</v>
+        <v>938.2524</v>
       </c>
       <c r="N32" t="n">
-        <v>958.8773</v>
+        <v>958.7264</v>
       </c>
       <c r="O32" t="n">
-        <v>581.3908</v>
+        <v>581.2993</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -10899,22 +10899,22 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>967.01</v>
+        <v>966.8578</v>
       </c>
       <c r="K33" t="n">
-        <v>968.71</v>
+        <v>968.5576</v>
       </c>
       <c r="L33" t="n">
-        <v>906.89</v>
+        <v>906.7473</v>
       </c>
       <c r="M33" t="n">
-        <v>935.39</v>
+        <v>935.2428</v>
       </c>
       <c r="N33" t="n">
-        <v>957.1731</v>
+        <v>957.0223999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>584.8792999999999</v>
+        <v>584.7873</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -11085,22 +11085,22 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>919.29</v>
+        <v>919.1453</v>
       </c>
       <c r="K34" t="n">
-        <v>946.8</v>
+        <v>946.651</v>
       </c>
       <c r="L34" t="n">
-        <v>909.09</v>
+        <v>908.947</v>
       </c>
       <c r="M34" t="n">
-        <v>932.86</v>
+        <v>932.7132</v>
       </c>
       <c r="N34" t="n">
-        <v>954.9697</v>
+        <v>954.8194</v>
       </c>
       <c r="O34" t="n">
-        <v>588.2784</v>
+        <v>588.1858</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>931.39</v>
+        <v>931.2434</v>
       </c>
       <c r="K35" t="n">
-        <v>959.97</v>
+        <v>959.8189</v>
       </c>
       <c r="L35" t="n">
-        <v>930.79</v>
+        <v>930.6435</v>
       </c>
       <c r="M35" t="n">
-        <v>958.73</v>
+        <v>958.5791</v>
       </c>
       <c r="N35" t="n">
-        <v>951.468</v>
+        <v>951.3182</v>
       </c>
       <c r="O35" t="n">
-        <v>591.8676</v>
+        <v>591.7745</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -11457,22 +11457,22 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>941.13</v>
+        <v>940.9819</v>
       </c>
       <c r="K36" t="n">
-        <v>969.4400000000001</v>
+        <v>969.2874</v>
       </c>
       <c r="L36" t="n">
-        <v>922.39</v>
+        <v>922.2448000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>933.4400000000001</v>
+        <v>933.2931</v>
       </c>
       <c r="N36" t="n">
-        <v>945.9129</v>
+        <v>945.764</v>
       </c>
       <c r="O36" t="n">
-        <v>595.3115</v>
+        <v>595.2179</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -11643,22 +11643,22 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>930.83</v>
+        <v>930.6835</v>
       </c>
       <c r="K37" t="n">
-        <v>958</v>
+        <v>957.8492</v>
       </c>
       <c r="L37" t="n">
-        <v>927.16</v>
+        <v>927.0141</v>
       </c>
       <c r="M37" t="n">
-        <v>956.08</v>
+        <v>955.9296000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>944.0023</v>
+        <v>943.8538</v>
       </c>
       <c r="O37" t="n">
-        <v>598.9083000000001</v>
+        <v>598.8141000000001</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -11829,22 +11829,22 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>956.91</v>
+        <v>956.7594</v>
       </c>
       <c r="K38" t="n">
-        <v>959.76</v>
+        <v>959.609</v>
       </c>
       <c r="L38" t="n">
-        <v>918.88</v>
+        <v>918.7354</v>
       </c>
       <c r="M38" t="n">
-        <v>958.16</v>
+        <v>958.0092</v>
       </c>
       <c r="N38" t="n">
-        <v>942.1985</v>
+        <v>942.0503</v>
       </c>
       <c r="O38" t="n">
-        <v>602.4662</v>
+        <v>602.3714</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -12015,22 +12015,22 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>971.34</v>
+        <v>971.1872</v>
       </c>
       <c r="K39" t="n">
-        <v>1017.77</v>
+        <v>1017.6099</v>
       </c>
       <c r="L39" t="n">
-        <v>969</v>
+        <v>968.8475</v>
       </c>
       <c r="M39" t="n">
-        <v>1016.59</v>
+        <v>1016.4301</v>
       </c>
       <c r="N39" t="n">
-        <v>938.2628999999999</v>
+        <v>938.1152</v>
       </c>
       <c r="O39" t="n">
-        <v>606.3406</v>
+        <v>606.2452</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -12201,22 +12201,22 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1036.4</v>
+        <v>1036.2369</v>
       </c>
       <c r="K40" t="n">
-        <v>1041.0699</v>
+        <v>1040.9061</v>
       </c>
       <c r="L40" t="n">
-        <v>997.62</v>
+        <v>997.463</v>
       </c>
       <c r="M40" t="n">
-        <v>1000.26</v>
+        <v>1000.1026</v>
       </c>
       <c r="N40" t="n">
-        <v>935.625</v>
+        <v>935.4777</v>
       </c>
       <c r="O40" t="n">
-        <v>610.2005</v>
+        <v>610.1045</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -12387,22 +12387,22 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>998.8099999999999</v>
+        <v>998.6528</v>
       </c>
       <c r="K41" t="n">
-        <v>1042.4</v>
+        <v>1042.236</v>
       </c>
       <c r="L41" t="n">
-        <v>992.29</v>
+        <v>992.1338</v>
       </c>
       <c r="M41" t="n">
-        <v>1027.77</v>
+        <v>1027.6083</v>
       </c>
       <c r="N41" t="n">
-        <v>933.2782999999999</v>
+        <v>933.1314</v>
       </c>
       <c r="O41" t="n">
-        <v>614.2109</v>
+        <v>614.1142</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -12573,22 +12573,22 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>997</v>
+        <v>996.8431</v>
       </c>
       <c r="K42" t="n">
-        <v>999</v>
+        <v>998.8428</v>
       </c>
       <c r="L42" t="n">
-        <v>973.5</v>
+        <v>973.3468</v>
       </c>
       <c r="M42" t="n">
-        <v>977.41</v>
+        <v>977.2562</v>
       </c>
       <c r="N42" t="n">
-        <v>929.7442</v>
+        <v>929.5979</v>
       </c>
       <c r="O42" t="n">
-        <v>618.092</v>
+        <v>617.9948000000001</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -12759,22 +12759,22 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>993.2</v>
+        <v>993.0436999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>993.99</v>
+        <v>993.8336</v>
       </c>
       <c r="L43" t="n">
-        <v>967.38</v>
+        <v>967.2278</v>
       </c>
       <c r="M43" t="n">
-        <v>975.26</v>
+        <v>975.1066</v>
       </c>
       <c r="N43" t="n">
-        <v>928.607</v>
+        <v>928.4609</v>
       </c>
       <c r="O43" t="n">
-        <v>621.9325</v>
+        <v>621.8346</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -12945,22 +12945,22 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>906.03</v>
+        <v>905.8875</v>
       </c>
       <c r="K44" t="n">
-        <v>932.21</v>
+        <v>932.0633</v>
       </c>
       <c r="L44" t="n">
-        <v>902.6</v>
+        <v>902.458</v>
       </c>
       <c r="M44" t="n">
-        <v>924.03</v>
+        <v>923.8846</v>
       </c>
       <c r="N44" t="n">
-        <v>927.5794</v>
+        <v>927.4334</v>
       </c>
       <c r="O44" t="n">
-        <v>625.4340999999999</v>
+        <v>625.3357</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -13131,22 +13131,22 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>937.5</v>
+        <v>937.3525</v>
       </c>
       <c r="K45" t="n">
-        <v>944.9400000000001</v>
+        <v>944.7913</v>
       </c>
       <c r="L45" t="n">
-        <v>920.13</v>
+        <v>919.9852</v>
       </c>
       <c r="M45" t="n">
-        <v>927.6</v>
+        <v>927.454</v>
       </c>
       <c r="N45" t="n">
-        <v>926.4364</v>
+        <v>926.2906</v>
       </c>
       <c r="O45" t="n">
-        <v>628.9505</v>
+        <v>628.8516</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -13317,22 +13317,22 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>934.23</v>
+        <v>934.083</v>
       </c>
       <c r="K46" t="n">
-        <v>941.2</v>
+        <v>941.0519</v>
       </c>
       <c r="L46" t="n">
-        <v>917.64</v>
+        <v>917.4956</v>
       </c>
       <c r="M46" t="n">
-        <v>926.55</v>
+        <v>926.4041999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>926.1998</v>
+        <v>926.0540999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>632.4331</v>
+        <v>632.3336</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -13503,22 +13503,22 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>954.5700000000001</v>
+        <v>954.4198</v>
       </c>
       <c r="K47" t="n">
-        <v>986.2</v>
+        <v>986.0448</v>
       </c>
       <c r="L47" t="n">
-        <v>953.5</v>
+        <v>953.35</v>
       </c>
       <c r="M47" t="n">
-        <v>977.5</v>
+        <v>977.3462</v>
       </c>
       <c r="N47" t="n">
-        <v>926.7738000000001</v>
+        <v>926.628</v>
       </c>
       <c r="O47" t="n">
-        <v>636.1394</v>
+        <v>636.0393</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -13689,22 +13689,22 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>984.72</v>
+        <v>984.5650000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>1016.44</v>
+        <v>1016.2801</v>
       </c>
       <c r="L48" t="n">
-        <v>977.83</v>
+        <v>977.6761</v>
       </c>
       <c r="M48" t="n">
-        <v>1015.8</v>
+        <v>1015.6401</v>
       </c>
       <c r="N48" t="n">
-        <v>927.2569999999999</v>
+        <v>927.1111</v>
       </c>
       <c r="O48" t="n">
-        <v>640.0173</v>
+        <v>639.9165</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -13875,22 +13875,22 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>1044.99</v>
+        <v>1044.8255</v>
       </c>
       <c r="K49" t="n">
-        <v>1064.49</v>
+        <v>1064.3225</v>
       </c>
       <c r="L49" t="n">
-        <v>1030.6801</v>
+        <v>1030.5178</v>
       </c>
       <c r="M49" t="n">
-        <v>1043.96</v>
+        <v>1043.7957</v>
       </c>
       <c r="N49" t="n">
-        <v>928.5502</v>
+        <v>928.4041</v>
       </c>
       <c r="O49" t="n">
-        <v>644.0408</v>
+        <v>643.9394</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -14061,22 +14061,22 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1032.85</v>
+        <v>1032.6875</v>
       </c>
       <c r="K50" t="n">
-        <v>1097.25</v>
+        <v>1097.0773</v>
       </c>
       <c r="L50" t="n">
-        <v>1030.02</v>
+        <v>1029.8579</v>
       </c>
       <c r="M50" t="n">
-        <v>1096.16</v>
+        <v>1095.9875</v>
       </c>
       <c r="N50" t="n">
-        <v>931.7334</v>
+        <v>931.5868</v>
       </c>
       <c r="O50" t="n">
-        <v>648.3519</v>
+        <v>648.2499</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -14247,22 +14247,22 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1100.0699</v>
+        <v>1099.8968</v>
       </c>
       <c r="K51" t="n">
-        <v>1105.5</v>
+        <v>1105.326</v>
       </c>
       <c r="L51" t="n">
-        <v>1064.25</v>
+        <v>1064.0825</v>
       </c>
       <c r="M51" t="n">
-        <v>1071.88</v>
+        <v>1071.7113</v>
       </c>
       <c r="N51" t="n">
-        <v>933.5086</v>
+        <v>933.3617</v>
       </c>
       <c r="O51" t="n">
-        <v>652.5792</v>
+        <v>652.4765</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -14433,22 +14433,22 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1049.75</v>
+        <v>1049.5848</v>
       </c>
       <c r="K52" t="n">
-        <v>1081.04</v>
+        <v>1080.8699</v>
       </c>
       <c r="L52" t="n">
-        <v>1044</v>
+        <v>1043.8357</v>
       </c>
       <c r="M52" t="n">
-        <v>1080.53</v>
+        <v>1080.36</v>
       </c>
       <c r="N52" t="n">
-        <v>937.0336</v>
+        <v>936.8862</v>
       </c>
       <c r="O52" t="n">
-        <v>656.7969000000001</v>
+        <v>656.6935</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -14619,22 +14619,22 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1095.83</v>
+        <v>1095.6575</v>
       </c>
       <c r="K53" t="n">
-        <v>1108.72</v>
+        <v>1108.5455</v>
       </c>
       <c r="L53" t="n">
-        <v>1073</v>
+        <v>1072.8312</v>
       </c>
       <c r="M53" t="n">
-        <v>1082.28</v>
+        <v>1082.1097</v>
       </c>
       <c r="N53" t="n">
-        <v>941.6152</v>
+        <v>941.467</v>
       </c>
       <c r="O53" t="n">
-        <v>660.9749</v>
+        <v>660.8709</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -14805,22 +14805,22 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1075.98</v>
+        <v>1075.8106</v>
       </c>
       <c r="K54" t="n">
-        <v>1084.8101</v>
+        <v>1084.6393</v>
       </c>
       <c r="L54" t="n">
-        <v>1032</v>
+        <v>1031.8376</v>
       </c>
       <c r="M54" t="n">
-        <v>1053.98</v>
+        <v>1053.8141</v>
       </c>
       <c r="N54" t="n">
-        <v>945.7157999999999</v>
+        <v>945.567</v>
       </c>
       <c r="O54" t="n">
-        <v>664.9838999999999</v>
+        <v>664.8792999999999</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -14991,22 +14991,22 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1076.6899</v>
+        <v>1076.5205</v>
       </c>
       <c r="K55" t="n">
-        <v>1082.66</v>
+        <v>1082.4897</v>
       </c>
       <c r="L55" t="n">
-        <v>1057.7</v>
+        <v>1057.5335</v>
       </c>
       <c r="M55" t="n">
-        <v>1065.08</v>
+        <v>1064.9124</v>
       </c>
       <c r="N55" t="n">
-        <v>949.7082</v>
+        <v>949.5588</v>
       </c>
       <c r="O55" t="n">
-        <v>668.9921000000001</v>
+        <v>668.8868</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -15177,22 +15177,22 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1076.76</v>
+        <v>1076.5906</v>
       </c>
       <c r="K56" t="n">
-        <v>1083.5</v>
+        <v>1083.3295</v>
       </c>
       <c r="L56" t="n">
-        <v>1062.36</v>
+        <v>1062.1928</v>
       </c>
       <c r="M56" t="n">
-        <v>1065.11</v>
+        <v>1064.9424</v>
       </c>
       <c r="N56" t="n">
-        <v>951.5940000000001</v>
+        <v>951.4443</v>
       </c>
       <c r="O56" t="n">
-        <v>673.0266</v>
+        <v>672.9207</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -15363,22 +15363,22 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1054.08</v>
+        <v>1053.914</v>
       </c>
       <c r="K57" t="n">
-        <v>1098.9</v>
+        <v>1098.7271</v>
       </c>
       <c r="L57" t="n">
-        <v>1022.9</v>
+        <v>1022.739</v>
       </c>
       <c r="M57" t="n">
-        <v>1097.39</v>
+        <v>1097.2173</v>
       </c>
       <c r="N57" t="n">
-        <v>954.3522</v>
+        <v>954.202</v>
       </c>
       <c r="O57" t="n">
-        <v>677.309</v>
+        <v>677.2024</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -15549,22 +15549,22 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1107.35</v>
+        <v>1107.1757</v>
       </c>
       <c r="K58" t="n">
-        <v>1108</v>
+        <v>1107.8256</v>
       </c>
       <c r="L58" t="n">
-        <v>1072.01</v>
+        <v>1071.8413</v>
       </c>
       <c r="M58" t="n">
-        <v>1074.89</v>
+        <v>1074.7208</v>
       </c>
       <c r="N58" t="n">
-        <v>956.0458</v>
+        <v>955.8954</v>
       </c>
       <c r="O58" t="n">
-        <v>681.4971</v>
+        <v>681.3899</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -15735,22 +15735,22 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1069.6801</v>
+        <v>1069.5117</v>
       </c>
       <c r="K59" t="n">
-        <v>1074.88</v>
+        <v>1074.7108</v>
       </c>
       <c r="L59" t="n">
-        <v>1055.5601</v>
+        <v>1055.3939</v>
       </c>
       <c r="M59" t="n">
-        <v>1063.96</v>
+        <v>1063.7925</v>
       </c>
       <c r="N59" t="n">
-        <v>958.9059999999999</v>
+        <v>958.7551</v>
       </c>
       <c r="O59" t="n">
-        <v>685.6555</v>
+        <v>685.5476</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -15921,22 +15921,22 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1064.48</v>
+        <v>1064.3125</v>
       </c>
       <c r="K60" t="n">
-        <v>1074.3101</v>
+        <v>1074.141</v>
       </c>
       <c r="L60" t="n">
-        <v>1045.26</v>
+        <v>1045.0955</v>
       </c>
       <c r="M60" t="n">
-        <v>1045.5601</v>
+        <v>1045.3955</v>
       </c>
       <c r="N60" t="n">
-        <v>961.8132000000001</v>
+        <v>961.6618</v>
       </c>
       <c r="O60" t="n">
-        <v>689.7568</v>
+        <v>689.6482999999999</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -16107,22 +16107,22 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1017.37</v>
+        <v>1017.21</v>
       </c>
       <c r="K61" t="n">
-        <v>1089.22</v>
+        <v>1089.0486</v>
       </c>
       <c r="L61" t="n">
-        <v>1011.42</v>
+        <v>1011.2609</v>
       </c>
       <c r="M61" t="n">
-        <v>1088</v>
+        <v>1087.8289</v>
       </c>
       <c r="N61" t="n">
-        <v>967.1626</v>
+        <v>967.0104</v>
       </c>
       <c r="O61" t="n">
-        <v>693.9553</v>
+        <v>693.8461</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -16293,22 +16293,22 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>1077.5</v>
+        <v>1077.3305</v>
       </c>
       <c r="K62" t="n">
-        <v>1088.5</v>
+        <v>1088.3288</v>
       </c>
       <c r="L62" t="n">
-        <v>1032.1</v>
+        <v>1031.9376</v>
       </c>
       <c r="M62" t="n">
-        <v>1035.84</v>
+        <v>1035.677</v>
       </c>
       <c r="N62" t="n">
-        <v>973.0993999999999</v>
+        <v>972.9463</v>
       </c>
       <c r="O62" t="n">
-        <v>697.8062</v>
+        <v>697.6964</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -16479,22 +16479,22 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>1054.17</v>
+        <v>1054.0042</v>
       </c>
       <c r="K63" t="n">
-        <v>1054.17</v>
+        <v>1054.0042</v>
       </c>
       <c r="L63" t="n">
-        <v>1017</v>
+        <v>1016.84</v>
       </c>
       <c r="M63" t="n">
-        <v>1029</v>
+        <v>1028.8381</v>
       </c>
       <c r="N63" t="n">
-        <v>976.1862</v>
+        <v>976.0326</v>
       </c>
       <c r="O63" t="n">
-        <v>701.5696</v>
+        <v>701.4592</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -16665,22 +16665,22 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1002.45</v>
+        <v>1002.2923</v>
       </c>
       <c r="K64" t="n">
-        <v>1002.67</v>
+        <v>1002.5122</v>
       </c>
       <c r="L64" t="n">
-        <v>978.5</v>
+        <v>978.346</v>
       </c>
       <c r="M64" t="n">
-        <v>989.04</v>
+        <v>988.8843000000001</v>
       </c>
       <c r="N64" t="n">
-        <v>979.5064</v>
+        <v>979.3523</v>
       </c>
       <c r="O64" t="n">
-        <v>705.1348</v>
+        <v>705.0238000000001</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -16851,22 +16851,22 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>934.0700000000001</v>
+        <v>933.9231</v>
       </c>
       <c r="K65" t="n">
-        <v>953.6</v>
+        <v>953.4499</v>
       </c>
       <c r="L65" t="n">
-        <v>929.03</v>
+        <v>928.8839</v>
       </c>
       <c r="M65" t="n">
-        <v>953.1900000000001</v>
+        <v>953.04</v>
       </c>
       <c r="N65" t="n">
-        <v>981.9802</v>
+        <v>981.8257</v>
       </c>
       <c r="O65" t="n">
-        <v>708.4687</v>
+        <v>708.3572</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -17023,13 +17023,13 @@
         <v>131.75</v>
       </c>
       <c r="E66" t="n">
-        <v>131.81</v>
+        <v>131.78</v>
       </c>
       <c r="F66" t="n">
-        <v>128.3144</v>
+        <v>128.3138</v>
       </c>
       <c r="G66" t="n">
-        <v>120.3867</v>
+        <v>120.3865</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -17037,22 +17037,22 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>934.3</v>
+        <v>934.5599999999999</v>
       </c>
       <c r="K66" t="n">
         <v>949.42</v>
       </c>
       <c r="L66" t="n">
-        <v>913.6</v>
+        <v>913.5599999999999</v>
       </c>
       <c r="M66" t="n">
         <v>914.13</v>
       </c>
       <c r="N66" t="n">
-        <v>982.4094</v>
+        <v>982.2577</v>
       </c>
       <c r="O66" t="n">
-        <v>711.6168</v>
+        <v>711.5056</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>576.41</v>
+        <v>576.49</v>
       </c>
       <c r="S66" t="n">
         <v>580.08</v>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="AP66" t="n">
-        <v>589.6525</v>
+        <v>589.5700000000001</v>
       </c>
       <c r="AQ66" t="n">
         <v>591.88</v>
@@ -17152,22 +17152,22 @@
         </is>
       </c>
       <c r="AX66" t="n">
-        <v>2496.2168</v>
+        <v>2496.6255</v>
       </c>
       <c r="AY66" t="n">
-        <v>2523.0505</v>
+        <v>2526.0706</v>
       </c>
       <c r="AZ66" t="n">
-        <v>2408.7908</v>
+        <v>2403.2107</v>
       </c>
       <c r="BA66" t="n">
-        <v>2422.78</v>
+        <v>2418.207</v>
       </c>
       <c r="BB66" t="n">
-        <v>2555.6653</v>
+        <v>2555.5739</v>
       </c>
       <c r="BC66" t="n">
-        <v>2140.4701</v>
+        <v>2140.4473</v>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -17175,22 +17175,22 @@
         </is>
       </c>
       <c r="BF66" t="n">
-        <v>83092.64840000001</v>
+        <v>83095.125</v>
       </c>
       <c r="BG66" t="n">
-        <v>84005.7188</v>
+        <v>84049.0625</v>
       </c>
       <c r="BH66" t="n">
-        <v>81469.35159999999</v>
+        <v>81345.88280000001</v>
       </c>
       <c r="BI66" t="n">
-        <v>81779.10159999999</v>
+        <v>81562.49219999999</v>
       </c>
       <c r="BJ66" t="n">
-        <v>81169.0453</v>
+        <v>81164.71309999999</v>
       </c>
       <c r="BK66" t="n">
-        <v>72206.0502</v>
+        <v>72204.96709999999</v>
       </c>
     </row>
   </sheetData>
